--- a/files/AFL_V2_goalscorers.xlsx
+++ b/files/AFL_V2_goalscorers.xlsx
@@ -1481,16 +1481,16 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>1.51381114346757</v>
+        <v>1.51613539098051</v>
       </c>
       <c r="F2" t="n">
         <v>1.28</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="H2" t="n">
-        <v>5.14</v>
+        <v>5.12</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>
@@ -1513,7 +1513,7 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>1.34524427972639</v>
+        <v>1.34726094667619</v>
       </c>
       <c r="F3" t="n">
         <v>1.35</v>
@@ -1522,7 +1522,7 @@
         <v>2.57</v>
       </c>
       <c r="H3" t="n">
-        <v>6.52</v>
+        <v>6.5</v>
       </c>
       <c r="I3" t="s">
         <v>13</v>
@@ -1545,16 +1545,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>1.10859112772821</v>
+        <v>1.11014120605024</v>
       </c>
       <c r="F4" t="n">
         <v>1.49</v>
       </c>
       <c r="G4" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="H4" t="n">
-        <v>9.87</v>
+        <v>9.84</v>
       </c>
       <c r="I4" t="s">
         <v>13</v>
@@ -1577,16 +1577,16 @@
         <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>1.06538524330885</v>
+        <v>1.06695946259624</v>
       </c>
       <c r="F5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G5" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="H5" t="n">
-        <v>10.79</v>
+        <v>10.75</v>
       </c>
       <c r="I5" t="s">
         <v>13</v>
@@ -1609,16 +1609,16 @@
         <v>18</v>
       </c>
       <c r="E6" t="n">
-        <v>0.680637734837064</v>
+        <v>0.681342118016117</v>
       </c>
       <c r="F6" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="G6" t="n">
-        <v>6.71</v>
+        <v>6.7</v>
       </c>
       <c r="H6" t="n">
-        <v>31.42</v>
+        <v>31.34</v>
       </c>
       <c r="I6" t="s">
         <v>13</v>
@@ -1641,16 +1641,16 @@
         <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>0.655658155115063</v>
+        <v>0.656318823590928</v>
       </c>
       <c r="F7" t="n">
         <v>2.08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.12</v>
+        <v>7.1</v>
       </c>
       <c r="H7" t="n">
-        <v>34.52</v>
+        <v>34.43</v>
       </c>
       <c r="I7" t="s">
         <v>13</v>
@@ -1673,16 +1673,16 @@
         <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>0.644428601716949</v>
+        <v>0.645213039700714</v>
       </c>
       <c r="F8" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="G8" t="n">
-        <v>7.31</v>
+        <v>7.3</v>
       </c>
       <c r="H8" t="n">
-        <v>36.06</v>
+        <v>35.95</v>
       </c>
       <c r="I8" t="s">
         <v>13</v>
@@ -1705,16 +1705,16 @@
         <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>0.599171724408163</v>
+        <v>0.600179682653485</v>
       </c>
       <c r="F9" t="n">
         <v>2.22</v>
       </c>
       <c r="G9" t="n">
-        <v>8.22</v>
+        <v>8.2</v>
       </c>
       <c r="H9" t="n">
-        <v>43.41</v>
+        <v>43.23</v>
       </c>
       <c r="I9" t="s">
         <v>13</v>
@@ -1737,16 +1737,16 @@
         <v>22</v>
       </c>
       <c r="E10" t="n">
-        <v>0.491225947875653</v>
+        <v>0.491819232967952</v>
       </c>
       <c r="F10" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="G10" t="n">
-        <v>11.42</v>
+        <v>11.4</v>
       </c>
       <c r="H10" t="n">
-        <v>72.83</v>
+        <v>72.6</v>
       </c>
       <c r="I10" t="s">
         <v>13</v>
@@ -1769,16 +1769,16 @@
         <v>23</v>
       </c>
       <c r="E11" t="n">
-        <v>0.430414378555135</v>
+        <v>0.431156656700401</v>
       </c>
       <c r="F11" t="n">
         <v>2.86</v>
       </c>
       <c r="G11" t="n">
-        <v>14.31</v>
+        <v>14.27</v>
       </c>
       <c r="H11" t="n">
-        <v>103.55</v>
+        <v>103.07</v>
       </c>
       <c r="I11" t="s">
         <v>13</v>
@@ -1801,16 +1801,16 @@
         <v>24</v>
       </c>
       <c r="E12" t="n">
-        <v>0.38205394994734</v>
+        <v>0.382713220138015</v>
       </c>
       <c r="F12" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="G12" t="n">
-        <v>17.6</v>
+        <v>17.55</v>
       </c>
       <c r="H12" t="n">
-        <v>142.89</v>
+        <v>142.22</v>
       </c>
       <c r="I12" t="s">
         <v>13</v>
@@ -1833,16 +1833,16 @@
         <v>25</v>
       </c>
       <c r="E13" t="n">
-        <v>0.317916487918839</v>
+        <v>0.318468725099546</v>
       </c>
       <c r="F13" t="n">
         <v>3.67</v>
       </c>
       <c r="G13" t="n">
-        <v>24.39</v>
+        <v>24.31</v>
       </c>
       <c r="H13" t="n">
-        <v>236.55</v>
+        <v>235.42</v>
       </c>
       <c r="I13" t="s">
         <v>13</v>
@@ -1865,16 +1865,16 @@
         <v>26</v>
       </c>
       <c r="E14" t="n">
-        <v>0.292407815882842</v>
+        <v>0.292899719717768</v>
       </c>
       <c r="F14" t="n">
         <v>3.94</v>
       </c>
       <c r="G14" t="n">
-        <v>28.36</v>
+        <v>28.27</v>
       </c>
       <c r="H14" t="n">
-        <v>298.35</v>
+        <v>296.95</v>
       </c>
       <c r="I14" t="s">
         <v>13</v>
@@ -1897,16 +1897,16 @@
         <v>27</v>
       </c>
       <c r="E15" t="n">
-        <v>0.248648650658741</v>
+        <v>0.249066940520245</v>
       </c>
       <c r="F15" t="n">
         <v>4.54</v>
       </c>
       <c r="G15" t="n">
-        <v>38.11</v>
+        <v>38</v>
       </c>
       <c r="H15" t="n">
-        <v>469.76</v>
+        <v>467.54</v>
       </c>
       <c r="I15" t="s">
         <v>13</v>
@@ -1929,16 +1929,16 @@
         <v>28</v>
       </c>
       <c r="E16" t="n">
-        <v>0.242102260577995</v>
+        <v>0.242534764946256</v>
       </c>
       <c r="F16" t="n">
-        <v>4.65</v>
+        <v>4.64</v>
       </c>
       <c r="G16" t="n">
-        <v>40.03</v>
+        <v>39.9</v>
       </c>
       <c r="H16" t="n">
-        <v>506.44</v>
+        <v>503.9</v>
       </c>
       <c r="I16" t="s">
         <v>13</v>
@@ -1961,16 +1961,16 @@
         <v>29</v>
       </c>
       <c r="E17" t="n">
-        <v>0.240271261632711</v>
+        <v>0.240697340296286</v>
       </c>
       <c r="F17" t="n">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="G17" t="n">
-        <v>40.6</v>
+        <v>40.46</v>
       </c>
       <c r="H17" t="n">
-        <v>517.41</v>
+        <v>514.82</v>
       </c>
       <c r="I17" t="s">
         <v>13</v>
@@ -1993,16 +1993,16 @@
         <v>30</v>
       </c>
       <c r="E18" t="n">
-        <v>0.234632233137249</v>
+        <v>0.235044588544733</v>
       </c>
       <c r="F18" t="n">
-        <v>4.78</v>
+        <v>4.77</v>
       </c>
       <c r="G18" t="n">
-        <v>42.41</v>
+        <v>42.28</v>
       </c>
       <c r="H18" t="n">
-        <v>553.3</v>
+        <v>550.56</v>
       </c>
       <c r="I18" t="s">
         <v>13</v>
@@ -2025,16 +2025,16 @@
         <v>31</v>
       </c>
       <c r="E19" t="n">
-        <v>0.218475094615917</v>
+        <v>0.218842624931593</v>
       </c>
       <c r="F19" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="G19" t="n">
-        <v>48.41</v>
+        <v>48.26</v>
       </c>
       <c r="H19" t="n">
-        <v>677.2</v>
+        <v>673.97</v>
       </c>
       <c r="I19" t="s">
         <v>13</v>
@@ -2057,16 +2057,16 @@
         <v>33</v>
       </c>
       <c r="E20" t="n">
-        <v>1.99996653326283</v>
+        <v>1.9977968320934</v>
       </c>
       <c r="F20" t="n">
         <v>1.16</v>
       </c>
       <c r="G20" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H20" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="I20" t="s">
         <v>13</v>
@@ -2089,7 +2089,7 @@
         <v>34</v>
       </c>
       <c r="E21" t="n">
-        <v>1.15114246225419</v>
+        <v>1.14957611910087</v>
       </c>
       <c r="F21" t="n">
         <v>1.46</v>
@@ -2098,7 +2098,7 @@
         <v>3.13</v>
       </c>
       <c r="H21" t="n">
-        <v>9.08</v>
+        <v>9.11</v>
       </c>
       <c r="I21" t="s">
         <v>13</v>
@@ -2121,7 +2121,7 @@
         <v>35</v>
       </c>
       <c r="E22" t="n">
-        <v>1.15087560275108</v>
+        <v>1.14933961871709</v>
       </c>
       <c r="F22" t="n">
         <v>1.46</v>
@@ -2130,7 +2130,7 @@
         <v>3.13</v>
       </c>
       <c r="H22" t="n">
-        <v>9.09</v>
+        <v>9.11</v>
       </c>
       <c r="I22" t="s">
         <v>13</v>
@@ -2153,7 +2153,7 @@
         <v>36</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1346832635884</v>
+        <v>1.13334206491664</v>
       </c>
       <c r="F23" t="n">
         <v>1.47</v>
@@ -2162,7 +2162,7 @@
         <v>3.19</v>
       </c>
       <c r="H23" t="n">
-        <v>9.38</v>
+        <v>9.4</v>
       </c>
       <c r="I23" t="s">
         <v>13</v>
@@ -2185,16 +2185,16 @@
         <v>37</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0857805210668</v>
+        <v>1.08477079587214</v>
       </c>
       <c r="F24" t="n">
         <v>1.51</v>
       </c>
       <c r="G24" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="H24" t="n">
-        <v>10.34</v>
+        <v>10.36</v>
       </c>
       <c r="I24" t="s">
         <v>13</v>
@@ -2217,7 +2217,7 @@
         <v>38</v>
       </c>
       <c r="E25" t="n">
-        <v>1.05698131771225</v>
+        <v>1.05551263633751</v>
       </c>
       <c r="F25" t="n">
         <v>1.53</v>
@@ -2226,7 +2226,7 @@
         <v>3.51</v>
       </c>
       <c r="H25" t="n">
-        <v>10.98</v>
+        <v>11.01</v>
       </c>
       <c r="I25" t="s">
         <v>13</v>
@@ -2249,16 +2249,16 @@
         <v>39</v>
       </c>
       <c r="E26" t="n">
-        <v>0.846333500491058</v>
+        <v>0.845119090983346</v>
       </c>
       <c r="F26" t="n">
         <v>1.75</v>
       </c>
       <c r="G26" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="H26" t="n">
-        <v>18.41</v>
+        <v>18.47</v>
       </c>
       <c r="I26" t="s">
         <v>13</v>
@@ -2281,16 +2281,16 @@
         <v>40</v>
       </c>
       <c r="E27" t="n">
-        <v>0.703583305175053</v>
+        <v>0.702936613350312</v>
       </c>
       <c r="F27" t="n">
         <v>1.98</v>
       </c>
       <c r="G27" t="n">
-        <v>6.37</v>
+        <v>6.38</v>
       </c>
       <c r="H27" t="n">
-        <v>28.92</v>
+        <v>28.99</v>
       </c>
       <c r="I27" t="s">
         <v>13</v>
@@ -2313,16 +2313,16 @@
         <v>41</v>
       </c>
       <c r="E28" t="n">
-        <v>0.696488281731039</v>
+        <v>0.695535588679218</v>
       </c>
       <c r="F28" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>6.47</v>
+        <v>6.48</v>
       </c>
       <c r="H28" t="n">
-        <v>29.66</v>
+        <v>29.76</v>
       </c>
       <c r="I28" t="s">
         <v>13</v>
@@ -2345,16 +2345,16 @@
         <v>42</v>
       </c>
       <c r="E29" t="n">
-        <v>0.686911783833426</v>
+        <v>0.685827282064823</v>
       </c>
       <c r="F29" t="n">
         <v>2.01</v>
       </c>
       <c r="G29" t="n">
-        <v>6.61</v>
+        <v>6.63</v>
       </c>
       <c r="H29" t="n">
-        <v>30.7</v>
+        <v>30.83</v>
       </c>
       <c r="I29" t="s">
         <v>13</v>
@@ -2377,16 +2377,16 @@
         <v>43</v>
       </c>
       <c r="E30" t="n">
-        <v>0.516399143683515</v>
+        <v>0.515908574660956</v>
       </c>
       <c r="F30" t="n">
         <v>2.48</v>
       </c>
       <c r="G30" t="n">
-        <v>10.5</v>
+        <v>10.52</v>
       </c>
       <c r="H30" t="n">
-        <v>63.85</v>
+        <v>64.01</v>
       </c>
       <c r="I30" t="s">
         <v>13</v>
@@ -2409,16 +2409,16 @@
         <v>44</v>
       </c>
       <c r="E31" t="n">
-        <v>0.510181019239827</v>
+        <v>0.509716441248058</v>
       </c>
       <c r="F31" t="n">
         <v>2.5</v>
       </c>
       <c r="G31" t="n">
-        <v>10.72</v>
+        <v>10.73</v>
       </c>
       <c r="H31" t="n">
-        <v>65.91</v>
+        <v>66.07</v>
       </c>
       <c r="I31" t="s">
         <v>13</v>
@@ -2441,16 +2441,16 @@
         <v>45</v>
       </c>
       <c r="E32" t="n">
-        <v>0.487884187779968</v>
+        <v>0.487450347643821</v>
       </c>
       <c r="F32" t="n">
         <v>2.59</v>
       </c>
       <c r="G32" t="n">
-        <v>11.55</v>
+        <v>11.57</v>
       </c>
       <c r="H32" t="n">
-        <v>74.15</v>
+        <v>74.33</v>
       </c>
       <c r="I32" t="s">
         <v>13</v>
@@ -2473,16 +2473,16 @@
         <v>46</v>
       </c>
       <c r="E33" t="n">
-        <v>0.394125893017811</v>
+        <v>0.393776889530407</v>
       </c>
       <c r="F33" t="n">
         <v>3.07</v>
       </c>
       <c r="G33" t="n">
-        <v>16.67</v>
+        <v>16.7</v>
       </c>
       <c r="H33" t="n">
-        <v>131.32</v>
+        <v>131.64</v>
       </c>
       <c r="I33" t="s">
         <v>13</v>
@@ -2505,16 +2505,16 @@
         <v>47</v>
       </c>
       <c r="E34" t="n">
-        <v>0.367053973033265</v>
+        <v>0.366726634623014</v>
       </c>
       <c r="F34" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="G34" t="n">
-        <v>18.89</v>
+        <v>18.92</v>
       </c>
       <c r="H34" t="n">
-        <v>159.37</v>
+        <v>159.76</v>
       </c>
       <c r="I34" t="s">
         <v>13</v>
@@ -2537,16 +2537,16 @@
         <v>48</v>
       </c>
       <c r="E35" t="n">
-        <v>0.287438619145633</v>
+        <v>0.287165558114907</v>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="G35" t="n">
-        <v>29.25</v>
+        <v>29.3</v>
       </c>
       <c r="H35" t="n">
-        <v>312.94</v>
+        <v>313.77</v>
       </c>
       <c r="I35" t="s">
         <v>13</v>
@@ -2569,16 +2569,16 @@
         <v>49</v>
       </c>
       <c r="E36" t="n">
-        <v>0.284618976827181</v>
+        <v>0.284372380691955</v>
       </c>
       <c r="F36" t="n">
         <v>4.04</v>
       </c>
       <c r="G36" t="n">
-        <v>29.78</v>
+        <v>29.83</v>
       </c>
       <c r="H36" t="n">
-        <v>321.66</v>
+        <v>322.44</v>
       </c>
       <c r="I36" t="s">
         <v>13</v>
@@ -2601,16 +2601,16 @@
         <v>50</v>
       </c>
       <c r="E37" t="n">
-        <v>0.210029534770214</v>
+        <v>0.209830010846054</v>
       </c>
       <c r="F37" t="n">
         <v>5.28</v>
       </c>
       <c r="G37" t="n">
-        <v>52.09</v>
+        <v>52.18</v>
       </c>
       <c r="H37" t="n">
-        <v>757.46</v>
+        <v>759.51</v>
       </c>
       <c r="I37" t="s">
         <v>13</v>
@@ -2633,7 +2633,7 @@
         <v>53</v>
       </c>
       <c r="E38" t="n">
-        <v>1.78365542509246</v>
+        <v>1.78379848100669</v>
       </c>
       <c r="F38" t="n">
         <v>1.2</v>
@@ -2665,7 +2665,7 @@
         <v>54</v>
       </c>
       <c r="E39" t="n">
-        <v>1.62251695601847</v>
+        <v>1.62265053642428</v>
       </c>
       <c r="F39" t="n">
         <v>1.25</v>
@@ -2697,7 +2697,7 @@
         <v>55</v>
       </c>
       <c r="E40" t="n">
-        <v>1.60005710216352</v>
+        <v>1.60013213982278</v>
       </c>
       <c r="F40" t="n">
         <v>1.25</v>
@@ -2729,7 +2729,7 @@
         <v>56</v>
       </c>
       <c r="E41" t="n">
-        <v>1.43741300649558</v>
+        <v>1.43748532499241</v>
       </c>
       <c r="F41" t="n">
         <v>1.31</v>
@@ -2761,7 +2761,7 @@
         <v>57</v>
       </c>
       <c r="E42" t="n">
-        <v>1.14040517121881</v>
+        <v>1.14043498863364</v>
       </c>
       <c r="F42" t="n">
         <v>1.47</v>
@@ -2793,13 +2793,13 @@
         <v>58</v>
       </c>
       <c r="E43" t="n">
-        <v>1.06629108436953</v>
+        <v>1.0662432270765</v>
       </c>
       <c r="F43" t="n">
         <v>1.53</v>
       </c>
       <c r="G43" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="H43" t="n">
         <v>10.77</v>
@@ -2825,7 +2825,7 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>0.954769941529156</v>
+        <v>0.954619958798151</v>
       </c>
       <c r="F44" t="n">
         <v>1.63</v>
@@ -2857,16 +2857,16 @@
         <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>0.566130892107736</v>
+        <v>0.566278786512451</v>
       </c>
       <c r="F45" t="n">
         <v>2.31</v>
       </c>
       <c r="G45" t="n">
-        <v>9.02</v>
+        <v>9.01</v>
       </c>
       <c r="H45" t="n">
-        <v>50.25</v>
+        <v>50.21</v>
       </c>
       <c r="I45" t="s">
         <v>13</v>
@@ -2889,7 +2889,7 @@
         <v>61</v>
       </c>
       <c r="E46" t="n">
-        <v>0.559677684420676</v>
+        <v>0.559824801949174</v>
       </c>
       <c r="F46" t="n">
         <v>2.33</v>
@@ -2898,7 +2898,7 @@
         <v>9.19</v>
       </c>
       <c r="H46" t="n">
-        <v>51.76</v>
+        <v>51.73</v>
       </c>
       <c r="I46" t="s">
         <v>13</v>
@@ -2921,7 +2921,7 @@
         <v>62</v>
       </c>
       <c r="E47" t="n">
-        <v>0.529828854730528</v>
+        <v>0.529949214206662</v>
       </c>
       <c r="F47" t="n">
         <v>2.43</v>
@@ -2930,7 +2930,7 @@
         <v>10.06</v>
       </c>
       <c r="H47" t="n">
-        <v>59.7</v>
+        <v>59.66</v>
       </c>
       <c r="I47" t="s">
         <v>13</v>
@@ -2953,7 +2953,7 @@
         <v>63</v>
       </c>
       <c r="E48" t="n">
-        <v>0.442879253358156</v>
+        <v>0.443001123207011</v>
       </c>
       <c r="F48" t="n">
         <v>2.79</v>
@@ -2962,7 +2962,7 @@
         <v>13.62</v>
       </c>
       <c r="H48" t="n">
-        <v>95.92</v>
+        <v>95.85</v>
       </c>
       <c r="I48" t="s">
         <v>13</v>
@@ -2985,16 +2985,16 @@
         <v>64</v>
       </c>
       <c r="E49" t="n">
-        <v>0.344576179645181</v>
+        <v>0.344673142664439</v>
       </c>
       <c r="F49" t="n">
         <v>3.43</v>
       </c>
       <c r="G49" t="n">
-        <v>21.12</v>
+        <v>21.11</v>
       </c>
       <c r="H49" t="n">
-        <v>189.47</v>
+        <v>189.33</v>
       </c>
       <c r="I49" t="s">
         <v>13</v>
@@ -3017,16 +3017,16 @@
         <v>65</v>
       </c>
       <c r="E50" t="n">
-        <v>0.324420361174029</v>
+        <v>0.32451421636572</v>
       </c>
       <c r="F50" t="n">
         <v>3.61</v>
       </c>
       <c r="G50" t="n">
-        <v>23.52</v>
+        <v>23.51</v>
       </c>
       <c r="H50" t="n">
-        <v>223.68</v>
+        <v>223.5</v>
       </c>
       <c r="I50" t="s">
         <v>13</v>
@@ -3049,16 +3049,16 @@
         <v>66</v>
       </c>
       <c r="E51" t="n">
-        <v>0.29864507455497</v>
+        <v>0.298749736550858</v>
       </c>
       <c r="F51" t="n">
         <v>3.87</v>
       </c>
       <c r="G51" t="n">
-        <v>27.3</v>
+        <v>27.28</v>
       </c>
       <c r="H51" t="n">
-        <v>281.33</v>
+        <v>281.06</v>
       </c>
       <c r="I51" t="s">
         <v>13</v>
@@ -3081,16 +3081,16 @@
         <v>67</v>
       </c>
       <c r="E52" t="n">
-        <v>0.271351099591445</v>
+        <v>0.271430730681305</v>
       </c>
       <c r="F52" t="n">
         <v>4.21</v>
       </c>
       <c r="G52" t="n">
-        <v>32.48</v>
+        <v>32.46</v>
       </c>
       <c r="H52" t="n">
-        <v>367.56</v>
+        <v>367.26</v>
       </c>
       <c r="I52" t="s">
         <v>13</v>
@@ -3113,16 +3113,16 @@
         <v>68</v>
       </c>
       <c r="E53" t="n">
-        <v>0.269878247847007</v>
+        <v>0.269939555199826</v>
       </c>
       <c r="F53" t="n">
         <v>4.23</v>
       </c>
       <c r="G53" t="n">
-        <v>32.81</v>
+        <v>32.79</v>
       </c>
       <c r="H53" t="n">
-        <v>373.21</v>
+        <v>372.97</v>
       </c>
       <c r="I53" t="s">
         <v>13</v>
@@ -3145,16 +3145,16 @@
         <v>69</v>
       </c>
       <c r="E54" t="n">
-        <v>0.196175226247703</v>
+        <v>0.19621979072782</v>
       </c>
       <c r="F54" t="n">
         <v>5.61</v>
       </c>
       <c r="G54" t="n">
-        <v>59.17</v>
+        <v>59.14</v>
       </c>
       <c r="H54" t="n">
-        <v>920.03</v>
+        <v>919.43</v>
       </c>
       <c r="I54" t="s">
         <v>13</v>
@@ -3177,16 +3177,16 @@
         <v>70</v>
       </c>
       <c r="E55" t="n">
-        <v>0.169814876533702</v>
+        <v>0.169853452819981</v>
       </c>
       <c r="F55" t="n">
         <v>6.4</v>
       </c>
       <c r="G55" t="n">
-        <v>77.61</v>
+        <v>77.57</v>
       </c>
       <c r="H55" t="n">
-        <v>1390.91</v>
+        <v>1390</v>
       </c>
       <c r="I55" t="s">
         <v>13</v>
@@ -3209,7 +3209,7 @@
         <v>72</v>
       </c>
       <c r="E56" t="n">
-        <v>2.27307547403726</v>
+        <v>2.27291584273111</v>
       </c>
       <c r="F56" t="n">
         <v>1.11</v>
@@ -3241,7 +3241,7 @@
         <v>73</v>
       </c>
       <c r="E57" t="n">
-        <v>1.66818849132798</v>
+        <v>1.66802423952758</v>
       </c>
       <c r="F57" t="n">
         <v>1.23</v>
@@ -3273,7 +3273,7 @@
         <v>74</v>
       </c>
       <c r="E58" t="n">
-        <v>1.40080205787563</v>
+        <v>1.40062832737612</v>
       </c>
       <c r="F58" t="n">
         <v>1.33</v>
@@ -3305,7 +3305,7 @@
         <v>75</v>
       </c>
       <c r="E59" t="n">
-        <v>1.26218429322884</v>
+        <v>1.26195093105089</v>
       </c>
       <c r="F59" t="n">
         <v>1.39</v>
@@ -3337,7 +3337,7 @@
         <v>76</v>
       </c>
       <c r="E60" t="n">
-        <v>0.951514514900314</v>
+        <v>0.951349025085441</v>
       </c>
       <c r="F60" t="n">
         <v>1.63</v>
@@ -3369,7 +3369,7 @@
         <v>77</v>
       </c>
       <c r="E61" t="n">
-        <v>0.900006184850799</v>
+        <v>0.899839633293228</v>
       </c>
       <c r="F61" t="n">
         <v>1.69</v>
@@ -3378,7 +3378,7 @@
         <v>4.4</v>
       </c>
       <c r="H61" t="n">
-        <v>15.91</v>
+        <v>15.92</v>
       </c>
       <c r="I61" t="s">
         <v>13</v>
@@ -3401,7 +3401,7 @@
         <v>78</v>
       </c>
       <c r="E62" t="n">
-        <v>0.782057551296671</v>
+        <v>0.781886118297629</v>
       </c>
       <c r="F62" t="n">
         <v>1.84</v>
@@ -3410,7 +3410,7 @@
         <v>5.41</v>
       </c>
       <c r="H62" t="n">
-        <v>22.28</v>
+        <v>22.29</v>
       </c>
       <c r="I62" t="s">
         <v>13</v>
@@ -3433,16 +3433,16 @@
         <v>79</v>
       </c>
       <c r="E63" t="n">
-        <v>0.69625431519354</v>
+        <v>0.695783262186059</v>
       </c>
       <c r="F63" t="n">
         <v>1.99</v>
       </c>
       <c r="G63" t="n">
-        <v>6.47</v>
+        <v>6.48</v>
       </c>
       <c r="H63" t="n">
-        <v>29.68</v>
+        <v>29.73</v>
       </c>
       <c r="I63" t="s">
         <v>13</v>
@@ -3465,7 +3465,7 @@
         <v>80</v>
       </c>
       <c r="E64" t="n">
-        <v>0.435488705957019</v>
+        <v>0.435537767742466</v>
       </c>
       <c r="F64" t="n">
         <v>2.83</v>
@@ -3474,7 +3474,7 @@
         <v>14.02</v>
       </c>
       <c r="H64" t="n">
-        <v>100.34</v>
+        <v>100.31</v>
       </c>
       <c r="I64" t="s">
         <v>13</v>
@@ -3497,7 +3497,7 @@
         <v>81</v>
       </c>
       <c r="E65" t="n">
-        <v>0.327462316224717</v>
+        <v>0.327495757596626</v>
       </c>
       <c r="F65" t="n">
         <v>3.58</v>
@@ -3506,7 +3506,7 @@
         <v>23.13</v>
       </c>
       <c r="H65" t="n">
-        <v>217.99</v>
+        <v>217.93</v>
       </c>
       <c r="I65" t="s">
         <v>13</v>
@@ -3529,7 +3529,7 @@
         <v>82</v>
       </c>
       <c r="E66" t="n">
-        <v>0.318701122346743</v>
+        <v>0.31874173142813</v>
       </c>
       <c r="F66" t="n">
         <v>3.66</v>
@@ -3538,7 +3538,7 @@
         <v>24.28</v>
       </c>
       <c r="H66" t="n">
-        <v>234.95</v>
+        <v>234.86</v>
       </c>
       <c r="I66" t="s">
         <v>13</v>
@@ -3561,16 +3561,16 @@
         <v>83</v>
       </c>
       <c r="E67" t="n">
-        <v>0.289212532788095</v>
+        <v>0.289228124206085</v>
       </c>
       <c r="F67" t="n">
         <v>3.98</v>
       </c>
       <c r="G67" t="n">
-        <v>28.93</v>
+        <v>28.92</v>
       </c>
       <c r="H67" t="n">
-        <v>307.62</v>
+        <v>307.57</v>
       </c>
       <c r="I67" t="s">
         <v>13</v>
@@ -3593,16 +3593,16 @@
         <v>84</v>
       </c>
       <c r="E68" t="n">
-        <v>0.279461311005112</v>
+        <v>0.279476376735735</v>
       </c>
       <c r="F68" t="n">
         <v>4.1</v>
       </c>
       <c r="G68" t="n">
-        <v>30.79</v>
+        <v>30.78</v>
       </c>
       <c r="H68" t="n">
-        <v>338.51</v>
+        <v>338.46</v>
       </c>
       <c r="I68" t="s">
         <v>13</v>
@@ -3625,16 +3625,16 @@
         <v>85</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2466788150608</v>
+        <v>0.246692113490428</v>
       </c>
       <c r="F69" t="n">
         <v>4.57</v>
       </c>
       <c r="G69" t="n">
-        <v>38.68</v>
+        <v>38.67</v>
       </c>
       <c r="H69" t="n">
-        <v>480.4</v>
+        <v>480.33</v>
       </c>
       <c r="I69" t="s">
         <v>13</v>
@@ -3657,7 +3657,7 @@
         <v>86</v>
       </c>
       <c r="E70" t="n">
-        <v>0.245445637718261</v>
+        <v>0.245476441300386</v>
       </c>
       <c r="F70" t="n">
         <v>4.59</v>
@@ -3666,7 +3666,7 @@
         <v>39.03</v>
       </c>
       <c r="H70" t="n">
-        <v>487.23</v>
+        <v>487.06</v>
       </c>
       <c r="I70" t="s">
         <v>13</v>
@@ -3689,16 +3689,16 @@
         <v>87</v>
       </c>
       <c r="E71" t="n">
-        <v>0.2356419026065</v>
+        <v>0.235675300692841</v>
       </c>
       <c r="F71" t="n">
         <v>4.76</v>
       </c>
       <c r="G71" t="n">
-        <v>42.08</v>
+        <v>42.07</v>
       </c>
       <c r="H71" t="n">
-        <v>546.62</v>
+        <v>546.41</v>
       </c>
       <c r="I71" t="s">
         <v>13</v>
@@ -3721,16 +3721,16 @@
         <v>88</v>
       </c>
       <c r="E72" t="n">
-        <v>0.210123609094484</v>
+        <v>0.210152321414834</v>
       </c>
       <c r="F72" t="n">
         <v>5.28</v>
       </c>
       <c r="G72" t="n">
-        <v>52.05</v>
+        <v>52.03</v>
       </c>
       <c r="H72" t="n">
-        <v>756.49</v>
+        <v>756.2</v>
       </c>
       <c r="I72" t="s">
         <v>13</v>
@@ -3753,16 +3753,16 @@
         <v>89</v>
       </c>
       <c r="E73" t="n">
-        <v>0.153956086592861</v>
+        <v>0.153964386349704</v>
       </c>
       <c r="F73" t="n">
         <v>7.01</v>
       </c>
       <c r="G73" t="n">
-        <v>93.44</v>
+        <v>93.43</v>
       </c>
       <c r="H73" t="n">
-        <v>1844.64</v>
+        <v>1844.36</v>
       </c>
       <c r="I73" t="s">
         <v>13</v>
@@ -3785,7 +3785,7 @@
         <v>92</v>
       </c>
       <c r="E74" t="n">
-        <v>1.21106868732022</v>
+        <v>1.21147902907502</v>
       </c>
       <c r="F74" t="n">
         <v>1.42</v>
@@ -3794,7 +3794,7 @@
         <v>2.93</v>
       </c>
       <c r="H74" t="n">
-        <v>8.14</v>
+        <v>8.13</v>
       </c>
       <c r="I74" t="s">
         <v>13</v>
@@ -3817,16 +3817,16 @@
         <v>93</v>
       </c>
       <c r="E75" t="n">
-        <v>1.00315248162894</v>
+        <v>1.00371229369865</v>
       </c>
       <c r="F75" t="n">
         <v>1.58</v>
       </c>
       <c r="G75" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="H75" t="n">
-        <v>12.36</v>
+        <v>12.35</v>
       </c>
       <c r="I75" t="s">
         <v>13</v>
@@ -3849,7 +3849,7 @@
         <v>94</v>
       </c>
       <c r="E76" t="n">
-        <v>0.867322393183396</v>
+        <v>0.867358148403263</v>
       </c>
       <c r="F76" t="n">
         <v>1.72</v>
@@ -3858,7 +3858,7 @@
         <v>4.64</v>
       </c>
       <c r="H76" t="n">
-        <v>17.37</v>
+        <v>17.36</v>
       </c>
       <c r="I76" t="s">
         <v>13</v>
@@ -3881,7 +3881,7 @@
         <v>95</v>
       </c>
       <c r="E77" t="n">
-        <v>0.709010300890367</v>
+        <v>0.709034397081739</v>
       </c>
       <c r="F77" t="n">
         <v>1.97</v>
@@ -3913,7 +3913,7 @@
         <v>96</v>
       </c>
       <c r="E78" t="n">
-        <v>0.667347183926424</v>
+        <v>0.667433289368539</v>
       </c>
       <c r="F78" t="n">
         <v>2.05</v>
@@ -3922,7 +3922,7 @@
         <v>6.92</v>
       </c>
       <c r="H78" t="n">
-        <v>33.01</v>
+        <v>33</v>
       </c>
       <c r="I78" t="s">
         <v>13</v>
@@ -3945,7 +3945,7 @@
         <v>97</v>
       </c>
       <c r="E79" t="n">
-        <v>0.617083761718777</v>
+        <v>0.617012904658901</v>
       </c>
       <c r="F79" t="n">
         <v>2.17</v>
@@ -3954,7 +3954,7 @@
         <v>7.84</v>
       </c>
       <c r="H79" t="n">
-        <v>40.26</v>
+        <v>40.28</v>
       </c>
       <c r="I79" t="s">
         <v>13</v>
@@ -3977,7 +3977,7 @@
         <v>98</v>
       </c>
       <c r="E80" t="n">
-        <v>0.607904486615774</v>
+        <v>0.607873245810125</v>
       </c>
       <c r="F80" t="n">
         <v>2.2</v>
@@ -4009,7 +4009,7 @@
         <v>99</v>
       </c>
       <c r="E81" t="n">
-        <v>0.595317531789673</v>
+        <v>0.595264839450189</v>
       </c>
       <c r="F81" t="n">
         <v>2.23</v>
@@ -4018,7 +4018,7 @@
         <v>8.31</v>
       </c>
       <c r="H81" t="n">
-        <v>44.14</v>
+        <v>44.15</v>
       </c>
       <c r="I81" t="s">
         <v>13</v>
@@ -4041,7 +4041,7 @@
         <v>100</v>
       </c>
       <c r="E82" t="n">
-        <v>0.498701125482944</v>
+        <v>0.498690539770832</v>
       </c>
       <c r="F82" t="n">
         <v>2.55</v>
@@ -4050,7 +4050,7 @@
         <v>11.13</v>
       </c>
       <c r="H82" t="n">
-        <v>69.98</v>
+        <v>69.99</v>
       </c>
       <c r="I82" t="s">
         <v>13</v>
@@ -4073,16 +4073,16 @@
         <v>101</v>
       </c>
       <c r="E83" t="n">
-        <v>0.357649639104965</v>
+        <v>0.357866526622082</v>
       </c>
       <c r="F83" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="G83" t="n">
-        <v>19.77</v>
+        <v>19.75</v>
       </c>
       <c r="H83" t="n">
-        <v>171.08</v>
+        <v>170.8</v>
       </c>
       <c r="I83" t="s">
         <v>13</v>
@@ -4105,16 +4105,16 @@
         <v>102</v>
       </c>
       <c r="E84" t="n">
-        <v>0.352577918898899</v>
+        <v>0.352790683686581</v>
       </c>
       <c r="F84" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="G84" t="n">
-        <v>20.28</v>
+        <v>20.26</v>
       </c>
       <c r="H84" t="n">
-        <v>177.91</v>
+        <v>177.61</v>
       </c>
       <c r="I84" t="s">
         <v>13</v>
@@ -4137,16 +4137,16 @@
         <v>103</v>
       </c>
       <c r="E85" t="n">
-        <v>0.230511930435308</v>
+        <v>0.230666603780007</v>
       </c>
       <c r="F85" t="n">
-        <v>4.86</v>
+        <v>4.85</v>
       </c>
       <c r="G85" t="n">
-        <v>43.83</v>
+        <v>43.77</v>
       </c>
       <c r="H85" t="n">
-        <v>581.72</v>
+        <v>580.62</v>
       </c>
       <c r="I85" t="s">
         <v>13</v>
@@ -4169,16 +4169,16 @@
         <v>104</v>
       </c>
       <c r="E86" t="n">
-        <v>0.145345876765342</v>
+        <v>0.145426987441522</v>
       </c>
       <c r="F86" t="n">
         <v>7.39</v>
       </c>
       <c r="G86" t="n">
-        <v>104.24</v>
+        <v>104.13</v>
       </c>
       <c r="H86" t="n">
-        <v>2178.27</v>
+        <v>2174.76</v>
       </c>
       <c r="I86" t="s">
         <v>13</v>
@@ -4201,16 +4201,16 @@
         <v>105</v>
       </c>
       <c r="E87" t="n">
-        <v>0.142264404287271</v>
+        <v>0.142343795339049</v>
       </c>
       <c r="F87" t="n">
         <v>7.54</v>
       </c>
       <c r="G87" t="n">
-        <v>108.59</v>
+        <v>108.47</v>
       </c>
       <c r="H87" t="n">
-        <v>2317.58</v>
+        <v>2313.84</v>
       </c>
       <c r="I87" t="s">
         <v>13</v>
@@ -4233,16 +4233,16 @@
         <v>106</v>
       </c>
       <c r="E88" t="n">
-        <v>0.100019125936006</v>
+        <v>0.100074941891133</v>
       </c>
       <c r="F88" t="n">
-        <v>10.51</v>
+        <v>10.5</v>
       </c>
       <c r="G88" t="n">
-        <v>213.65</v>
+        <v>213.42</v>
       </c>
       <c r="H88" t="n">
-        <v>6462.47</v>
+        <v>6451.93</v>
       </c>
       <c r="I88" t="s">
         <v>13</v>
@@ -4265,16 +4265,16 @@
         <v>107</v>
       </c>
       <c r="E89" t="n">
-        <v>0.0915272764800071</v>
+        <v>0.091578353534612</v>
       </c>
       <c r="F89" t="n">
         <v>11.43</v>
       </c>
       <c r="G89" t="n">
-        <v>253.7</v>
+        <v>253.43</v>
       </c>
       <c r="H89" t="n">
-        <v>8379.99</v>
+        <v>8366.29</v>
       </c>
       <c r="I89" t="s">
         <v>13</v>
@@ -4297,16 +4297,16 @@
         <v>108</v>
       </c>
       <c r="E90" t="n">
-        <v>0.0820895767455402</v>
+        <v>0.0821353870652086</v>
       </c>
       <c r="F90" t="n">
-        <v>12.69</v>
+        <v>12.68</v>
       </c>
       <c r="G90" t="n">
-        <v>313.43</v>
+        <v>313.09</v>
       </c>
       <c r="H90" t="n">
-        <v>11533.75</v>
+        <v>11514.85</v>
       </c>
       <c r="I90" t="s">
         <v>13</v>
@@ -4329,16 +4329,16 @@
         <v>109</v>
       </c>
       <c r="E91" t="n">
-        <v>0.0779945278195504</v>
+        <v>0.0780380528856239</v>
       </c>
       <c r="F91" t="n">
-        <v>13.33</v>
+        <v>13.32</v>
       </c>
       <c r="G91" t="n">
-        <v>346.27</v>
+        <v>345.89</v>
       </c>
       <c r="H91" t="n">
-        <v>13406.44</v>
+        <v>13384.46</v>
       </c>
       <c r="I91" t="s">
         <v>13</v>
@@ -4361,7 +4361,7 @@
         <v>111</v>
       </c>
       <c r="E92" t="n">
-        <v>2.25820845656544</v>
+        <v>2.25800863200733</v>
       </c>
       <c r="F92" t="n">
         <v>1.12</v>
@@ -4393,7 +4393,7 @@
         <v>112</v>
       </c>
       <c r="E93" t="n">
-        <v>1.82842902751644</v>
+        <v>1.82822982506333</v>
       </c>
       <c r="F93" t="n">
         <v>1.19</v>
@@ -4425,7 +4425,7 @@
         <v>113</v>
       </c>
       <c r="E94" t="n">
-        <v>1.71011992875817</v>
+        <v>1.7098873763378</v>
       </c>
       <c r="F94" t="n">
         <v>1.22</v>
@@ -4434,7 +4434,7 @@
         <v>1.96</v>
       </c>
       <c r="H94" t="n">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="I94" t="s">
         <v>13</v>
@@ -4457,7 +4457,7 @@
         <v>114</v>
       </c>
       <c r="E95" t="n">
-        <v>1.50088830969636</v>
+        <v>1.50018892890678</v>
       </c>
       <c r="F95" t="n">
         <v>1.29</v>
@@ -4489,7 +4489,7 @@
         <v>115</v>
       </c>
       <c r="E96" t="n">
-        <v>1.40339756244072</v>
+        <v>1.40314654443206</v>
       </c>
       <c r="F96" t="n">
         <v>1.33</v>
@@ -4521,7 +4521,7 @@
         <v>116</v>
       </c>
       <c r="E97" t="n">
-        <v>1.35029007390136</v>
+        <v>1.34980144423999</v>
       </c>
       <c r="F97" t="n">
         <v>1.35</v>
@@ -4553,7 +4553,7 @@
         <v>117</v>
       </c>
       <c r="E98" t="n">
-        <v>1.3312631272927</v>
+        <v>1.3313995661253</v>
       </c>
       <c r="F98" t="n">
         <v>1.36</v>
@@ -4585,7 +4585,7 @@
         <v>118</v>
       </c>
       <c r="E99" t="n">
-        <v>1.13818930691707</v>
+        <v>1.13793465363255</v>
       </c>
       <c r="F99" t="n">
         <v>1.47</v>
@@ -4594,7 +4594,7 @@
         <v>3.18</v>
       </c>
       <c r="H99" t="n">
-        <v>9.31</v>
+        <v>9.32</v>
       </c>
       <c r="I99" t="s">
         <v>13</v>
@@ -4617,7 +4617,7 @@
         <v>119</v>
       </c>
       <c r="E100" t="n">
-        <v>0.980690006413569</v>
+        <v>0.980393885243755</v>
       </c>
       <c r="F100" t="n">
         <v>1.6</v>
@@ -4626,7 +4626,7 @@
         <v>3.89</v>
       </c>
       <c r="H100" t="n">
-        <v>13.02</v>
+        <v>13.03</v>
       </c>
       <c r="I100" t="s">
         <v>13</v>
@@ -4649,7 +4649,7 @@
         <v>120</v>
       </c>
       <c r="E101" t="n">
-        <v>0.535013904619693</v>
+        <v>0.535087959076013</v>
       </c>
       <c r="F101" t="n">
         <v>2.41</v>
@@ -4658,7 +4658,7 @@
         <v>9.9</v>
       </c>
       <c r="H101" t="n">
-        <v>58.2</v>
+        <v>58.18</v>
       </c>
       <c r="I101" t="s">
         <v>13</v>
@@ -4681,16 +4681,16 @@
         <v>121</v>
       </c>
       <c r="E102" t="n">
-        <v>0.433245562639357</v>
+        <v>0.433311434694966</v>
       </c>
       <c r="F102" t="n">
         <v>2.84</v>
       </c>
       <c r="G102" t="n">
-        <v>14.15</v>
+        <v>14.14</v>
       </c>
       <c r="H102" t="n">
-        <v>101.74</v>
+        <v>101.7</v>
       </c>
       <c r="I102" t="s">
         <v>13</v>
@@ -4713,7 +4713,7 @@
         <v>122</v>
       </c>
       <c r="E103" t="n">
-        <v>0.430695350015619</v>
+        <v>0.430757209086018</v>
       </c>
       <c r="F103" t="n">
         <v>2.86</v>
@@ -4722,7 +4722,7 @@
         <v>14.29</v>
       </c>
       <c r="H103" t="n">
-        <v>103.37</v>
+        <v>103.33</v>
       </c>
       <c r="I103" t="s">
         <v>13</v>
@@ -4745,16 +4745,16 @@
         <v>123</v>
       </c>
       <c r="E104" t="n">
-        <v>0.321859201995858</v>
+        <v>0.321910274623967</v>
       </c>
       <c r="F104" t="n">
         <v>3.63</v>
       </c>
       <c r="G104" t="n">
-        <v>23.86</v>
+        <v>23.85</v>
       </c>
       <c r="H104" t="n">
-        <v>228.63</v>
+        <v>228.53</v>
       </c>
       <c r="I104" t="s">
         <v>13</v>
@@ -4777,7 +4777,7 @@
         <v>124</v>
       </c>
       <c r="E105" t="n">
-        <v>0.291743615680027</v>
+        <v>0.291796130050184</v>
       </c>
       <c r="F105" t="n">
         <v>3.95</v>
@@ -4786,7 +4786,7 @@
         <v>28.47</v>
       </c>
       <c r="H105" t="n">
-        <v>300.24</v>
+        <v>300.09</v>
       </c>
       <c r="I105" t="s">
         <v>13</v>
@@ -4809,7 +4809,7 @@
         <v>125</v>
       </c>
       <c r="E106" t="n">
-        <v>0.257752139592647</v>
+        <v>0.257773240762</v>
       </c>
       <c r="F106" t="n">
         <v>4.4</v>
@@ -4818,7 +4818,7 @@
         <v>35.68</v>
       </c>
       <c r="H106" t="n">
-        <v>424.57</v>
+        <v>424.47</v>
       </c>
       <c r="I106" t="s">
         <v>13</v>
@@ -4841,16 +4841,16 @@
         <v>126</v>
       </c>
       <c r="E107" t="n">
-        <v>0.213311213741824</v>
+        <v>0.213328676704705</v>
       </c>
       <c r="F107" t="n">
         <v>5.21</v>
       </c>
       <c r="G107" t="n">
-        <v>50.61</v>
+        <v>50.6</v>
       </c>
       <c r="H107" t="n">
-        <v>724.79</v>
+        <v>724.63</v>
       </c>
       <c r="I107" t="s">
         <v>13</v>
@@ -4873,16 +4873,16 @@
         <v>127</v>
       </c>
       <c r="E108" t="n">
-        <v>0.202466056998784</v>
+        <v>0.202482632110687</v>
       </c>
       <c r="F108" t="n">
         <v>5.46</v>
       </c>
       <c r="G108" t="n">
-        <v>55.78</v>
+        <v>55.77</v>
       </c>
       <c r="H108" t="n">
-        <v>840.82</v>
+        <v>840.63</v>
       </c>
       <c r="I108" t="s">
         <v>13</v>
@@ -4905,16 +4905,16 @@
         <v>128</v>
       </c>
       <c r="E109" t="n">
-        <v>0.182115865993186</v>
+        <v>0.182130775113771</v>
       </c>
       <c r="F109" t="n">
         <v>6.01</v>
       </c>
       <c r="G109" t="n">
-        <v>68.02</v>
+        <v>68.01</v>
       </c>
       <c r="H109" t="n">
-        <v>1138.03</v>
+        <v>1137.76</v>
       </c>
       <c r="I109" t="s">
         <v>13</v>
@@ -4937,7 +4937,7 @@
         <v>131</v>
       </c>
       <c r="E110" t="n">
-        <v>1.78900623723813</v>
+        <v>1.78883065971307</v>
       </c>
       <c r="F110" t="n">
         <v>1.2</v>
@@ -4969,7 +4969,7 @@
         <v>132</v>
       </c>
       <c r="E111" t="n">
-        <v>1.65902597931022</v>
+        <v>1.6588527856269</v>
       </c>
       <c r="F111" t="n">
         <v>1.24</v>
@@ -5001,7 +5001,7 @@
         <v>133</v>
       </c>
       <c r="E112" t="n">
-        <v>1.5842524137416</v>
+        <v>1.58401846704878</v>
       </c>
       <c r="F112" t="n">
         <v>1.26</v>
@@ -5010,7 +5010,7 @@
         <v>2.13</v>
       </c>
       <c r="H112" t="n">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="I112" t="s">
         <v>13</v>
@@ -5033,7 +5033,7 @@
         <v>134</v>
       </c>
       <c r="E113" t="n">
-        <v>1.21932129159191</v>
+        <v>1.21910488174206</v>
       </c>
       <c r="F113" t="n">
         <v>1.42</v>
@@ -5065,7 +5065,7 @@
         <v>135</v>
       </c>
       <c r="E114" t="n">
-        <v>1.08913579307909</v>
+        <v>1.08885172487367</v>
       </c>
       <c r="F114" t="n">
         <v>1.51</v>
@@ -5097,7 +5097,7 @@
         <v>136</v>
       </c>
       <c r="E115" t="n">
-        <v>0.864640234741791</v>
+        <v>0.864697664635552</v>
       </c>
       <c r="F115" t="n">
         <v>1.73</v>
@@ -5129,7 +5129,7 @@
         <v>137</v>
       </c>
       <c r="E116" t="n">
-        <v>0.846525292486517</v>
+        <v>0.846277816207525</v>
       </c>
       <c r="F116" t="n">
         <v>1.75</v>
@@ -5138,7 +5138,7 @@
         <v>4.81</v>
       </c>
       <c r="H116" t="n">
-        <v>18.4</v>
+        <v>18.41</v>
       </c>
       <c r="I116" t="s">
         <v>13</v>
@@ -5161,7 +5161,7 @@
         <v>138</v>
       </c>
       <c r="E117" t="n">
-        <v>0.845703160519456</v>
+        <v>0.845741616745546</v>
       </c>
       <c r="F117" t="n">
         <v>1.75</v>
@@ -5193,7 +5193,7 @@
         <v>139</v>
       </c>
       <c r="E118" t="n">
-        <v>0.744937418777094</v>
+        <v>0.74470653755096</v>
       </c>
       <c r="F118" t="n">
         <v>1.9</v>
@@ -5202,7 +5202,7 @@
         <v>5.83</v>
       </c>
       <c r="H118" t="n">
-        <v>25.1</v>
+        <v>25.12</v>
       </c>
       <c r="I118" t="s">
         <v>13</v>
@@ -5225,7 +5225,7 @@
         <v>140</v>
       </c>
       <c r="E119" t="n">
-        <v>0.395441561272928</v>
+        <v>0.395479451939577</v>
       </c>
       <c r="F119" t="n">
         <v>3.06</v>
@@ -5234,7 +5234,7 @@
         <v>16.57</v>
       </c>
       <c r="H119" t="n">
-        <v>130.14</v>
+        <v>130.1</v>
       </c>
       <c r="I119" t="s">
         <v>13</v>
@@ -5257,7 +5257,7 @@
         <v>141</v>
       </c>
       <c r="E120" t="n">
-        <v>0.336532623076542</v>
+        <v>0.336547926051916</v>
       </c>
       <c r="F120" t="n">
         <v>3.5</v>
@@ -5266,7 +5266,7 @@
         <v>22.03</v>
       </c>
       <c r="H120" t="n">
-        <v>202.18</v>
+        <v>202.16</v>
       </c>
       <c r="I120" t="s">
         <v>13</v>
@@ -5289,16 +5289,16 @@
         <v>142</v>
       </c>
       <c r="E121" t="n">
-        <v>0.324156299821521</v>
+        <v>0.324197397951412</v>
       </c>
       <c r="F121" t="n">
         <v>3.61</v>
       </c>
       <c r="G121" t="n">
-        <v>23.56</v>
+        <v>23.55</v>
       </c>
       <c r="H121" t="n">
-        <v>224.18</v>
+        <v>224.1</v>
       </c>
       <c r="I121" t="s">
         <v>13</v>
@@ -5321,7 +5321,7 @@
         <v>143</v>
       </c>
       <c r="E122" t="n">
-        <v>0.307647555061358</v>
+        <v>0.307679670498537</v>
       </c>
       <c r="F122" t="n">
         <v>3.78</v>
@@ -5330,7 +5330,7 @@
         <v>25.87</v>
       </c>
       <c r="H122" t="n">
-        <v>259.07</v>
+        <v>258.99</v>
       </c>
       <c r="I122" t="s">
         <v>13</v>
@@ -5353,7 +5353,7 @@
         <v>144</v>
       </c>
       <c r="E123" t="n">
-        <v>0.306086978783765</v>
+        <v>0.30612297779303</v>
       </c>
       <c r="F123" t="n">
         <v>3.79</v>
@@ -5362,7 +5362,7 @@
         <v>26.11</v>
       </c>
       <c r="H123" t="n">
-        <v>262.75</v>
+        <v>262.66</v>
       </c>
       <c r="I123" t="s">
         <v>13</v>
@@ -5385,16 +5385,16 @@
         <v>145</v>
       </c>
       <c r="E124" t="n">
-        <v>0.271546945732338</v>
+        <v>0.271580919132481</v>
       </c>
       <c r="F124" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="G124" t="n">
-        <v>32.44</v>
+        <v>32.43</v>
       </c>
       <c r="H124" t="n">
-        <v>366.82</v>
+        <v>366.69</v>
       </c>
       <c r="I124" t="s">
         <v>13</v>
@@ -5417,16 +5417,16 @@
         <v>146</v>
       </c>
       <c r="E125" t="n">
-        <v>0.183728783293214</v>
+        <v>0.183760791969835</v>
       </c>
       <c r="F125" t="n">
         <v>5.96</v>
       </c>
       <c r="G125" t="n">
-        <v>66.91</v>
+        <v>66.88</v>
       </c>
       <c r="H125" t="n">
-        <v>1109.65</v>
+        <v>1109.1</v>
       </c>
       <c r="I125" t="s">
         <v>13</v>
@@ -5449,16 +5449,16 @@
         <v>147</v>
       </c>
       <c r="E126" t="n">
-        <v>0.154261142575928</v>
+        <v>0.15426815721375</v>
       </c>
       <c r="F126" t="n">
         <v>7</v>
       </c>
       <c r="G126" t="n">
-        <v>93.09</v>
+        <v>93.08</v>
       </c>
       <c r="H126" t="n">
-        <v>1834.14</v>
+        <v>1833.9</v>
       </c>
       <c r="I126" t="s">
         <v>13</v>
@@ -5481,16 +5481,16 @@
         <v>148</v>
       </c>
       <c r="E127" t="n">
-        <v>0.102659060361675</v>
+        <v>0.102663728524477</v>
       </c>
       <c r="F127" t="n">
         <v>10.25</v>
       </c>
       <c r="G127" t="n">
-        <v>203.16</v>
+        <v>203.14</v>
       </c>
       <c r="H127" t="n">
-        <v>5988.41</v>
+        <v>5987.61</v>
       </c>
       <c r="I127" t="s">
         <v>13</v>
@@ -5513,7 +5513,7 @@
         <v>150</v>
       </c>
       <c r="E128" t="n">
-        <v>1.37443197280739</v>
+        <v>1.37458569938787</v>
       </c>
       <c r="F128" t="n">
         <v>1.34</v>
@@ -5522,7 +5522,7 @@
         <v>2.5</v>
       </c>
       <c r="H128" t="n">
-        <v>6.24</v>
+        <v>6.23</v>
       </c>
       <c r="I128" t="s">
         <v>13</v>
@@ -5545,7 +5545,7 @@
         <v>151</v>
       </c>
       <c r="E129" t="n">
-        <v>1.2918425411144</v>
+        <v>1.29199948744332</v>
       </c>
       <c r="F129" t="n">
         <v>1.38</v>
@@ -5577,16 +5577,16 @@
         <v>152</v>
       </c>
       <c r="E130" t="n">
-        <v>1.01518865784657</v>
+        <v>1.01550779018311</v>
       </c>
       <c r="F130" t="n">
         <v>1.57</v>
       </c>
       <c r="G130" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="H130" t="n">
-        <v>12.03</v>
+        <v>12.02</v>
       </c>
       <c r="I130" t="s">
         <v>13</v>
@@ -5609,10 +5609,10 @@
         <v>153</v>
       </c>
       <c r="E131" t="n">
-        <v>0.891535387523654</v>
+        <v>0.891510052177326</v>
       </c>
       <c r="F131" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G131" t="n">
         <v>4.46</v>
@@ -5641,7 +5641,7 @@
         <v>154</v>
       </c>
       <c r="E132" t="n">
-        <v>0.881333183378775</v>
+        <v>0.881239886066207</v>
       </c>
       <c r="F132" t="n">
         <v>1.71</v>
@@ -5673,7 +5673,7 @@
         <v>155</v>
       </c>
       <c r="E133" t="n">
-        <v>0.749537550129479</v>
+        <v>0.749543763127755</v>
       </c>
       <c r="F133" t="n">
         <v>1.9</v>
@@ -5705,7 +5705,7 @@
         <v>156</v>
       </c>
       <c r="E134" t="n">
-        <v>0.641832260886132</v>
+        <v>0.641643371294221</v>
       </c>
       <c r="F134" t="n">
         <v>2.11</v>
@@ -5714,7 +5714,7 @@
         <v>7.36</v>
       </c>
       <c r="H134" t="n">
-        <v>36.43</v>
+        <v>36.46</v>
       </c>
       <c r="I134" t="s">
         <v>13</v>
@@ -5737,16 +5737,16 @@
         <v>157</v>
       </c>
       <c r="E135" t="n">
-        <v>0.630335333657752</v>
+        <v>0.630543528676216</v>
       </c>
       <c r="F135" t="n">
         <v>2.14</v>
       </c>
       <c r="G135" t="n">
-        <v>7.58</v>
+        <v>7.57</v>
       </c>
       <c r="H135" t="n">
-        <v>38.14</v>
+        <v>38.11</v>
       </c>
       <c r="I135" t="s">
         <v>13</v>
@@ -5769,7 +5769,7 @@
         <v>158</v>
       </c>
       <c r="E136" t="n">
-        <v>0.609830591361404</v>
+        <v>0.609704267057993</v>
       </c>
       <c r="F136" t="n">
         <v>2.19</v>
@@ -5778,7 +5778,7 @@
         <v>7.99</v>
       </c>
       <c r="H136" t="n">
-        <v>41.5</v>
+        <v>41.52</v>
       </c>
       <c r="I136" t="s">
         <v>13</v>
@@ -5801,7 +5801,7 @@
         <v>159</v>
       </c>
       <c r="E137" t="n">
-        <v>0.608266096354695</v>
+        <v>0.608447268371338</v>
       </c>
       <c r="F137" t="n">
         <v>2.19</v>
@@ -5810,7 +5810,7 @@
         <v>8.02</v>
       </c>
       <c r="H137" t="n">
-        <v>41.77</v>
+        <v>41.74</v>
       </c>
       <c r="I137" t="s">
         <v>13</v>
@@ -5833,16 +5833,16 @@
         <v>160</v>
       </c>
       <c r="E138" t="n">
-        <v>0.607774050816055</v>
+        <v>0.607620107256993</v>
       </c>
       <c r="F138" t="n">
         <v>2.2</v>
       </c>
       <c r="G138" t="n">
-        <v>8.03</v>
+        <v>8.04</v>
       </c>
       <c r="H138" t="n">
-        <v>41.86</v>
+        <v>41.89</v>
       </c>
       <c r="I138" t="s">
         <v>13</v>
@@ -5865,16 +5865,16 @@
         <v>161</v>
       </c>
       <c r="E139" t="n">
-        <v>0.402477717215337</v>
+        <v>0.40259759517684</v>
       </c>
       <c r="F139" t="n">
         <v>3.02</v>
       </c>
       <c r="G139" t="n">
-        <v>16.07</v>
+        <v>16.06</v>
       </c>
       <c r="H139" t="n">
-        <v>124.07</v>
+        <v>123.97</v>
       </c>
       <c r="I139" t="s">
         <v>13</v>
@@ -5897,16 +5897,16 @@
         <v>162</v>
       </c>
       <c r="E140" t="n">
-        <v>0.385118484033602</v>
+        <v>0.385249941774244</v>
       </c>
       <c r="F140" t="n">
         <v>3.13</v>
       </c>
       <c r="G140" t="n">
-        <v>17.36</v>
+        <v>17.35</v>
       </c>
       <c r="H140" t="n">
-        <v>139.82</v>
+        <v>139.69</v>
       </c>
       <c r="I140" t="s">
         <v>13</v>
@@ -5929,16 +5929,16 @@
         <v>163</v>
       </c>
       <c r="E141" t="n">
-        <v>0.380374331448174</v>
+        <v>0.380505316049103</v>
       </c>
       <c r="F141" t="n">
         <v>3.16</v>
       </c>
       <c r="G141" t="n">
-        <v>17.74</v>
+        <v>17.73</v>
       </c>
       <c r="H141" t="n">
-        <v>144.61</v>
+        <v>144.48</v>
       </c>
       <c r="I141" t="s">
         <v>13</v>
@@ -5961,16 +5961,16 @@
         <v>164</v>
       </c>
       <c r="E142" t="n">
-        <v>0.261136441181371</v>
+        <v>0.261245353292283</v>
       </c>
       <c r="F142" t="n">
         <v>4.35</v>
       </c>
       <c r="G142" t="n">
-        <v>34.84</v>
+        <v>34.81</v>
       </c>
       <c r="H142" t="n">
-        <v>409.3</v>
+        <v>408.82</v>
       </c>
       <c r="I142" t="s">
         <v>13</v>
@@ -5993,16 +5993,16 @@
         <v>165</v>
       </c>
       <c r="E143" t="n">
-        <v>0.225962817366282</v>
+        <v>0.226047071161826</v>
       </c>
       <c r="F143" t="n">
         <v>4.94</v>
       </c>
       <c r="G143" t="n">
-        <v>45.47</v>
+        <v>45.44</v>
       </c>
       <c r="H143" t="n">
-        <v>615.49</v>
+        <v>614.84</v>
       </c>
       <c r="I143" t="s">
         <v>13</v>
@@ -6025,16 +6025,16 @@
         <v>166</v>
       </c>
       <c r="E144" t="n">
-        <v>0.171433496451016</v>
+        <v>0.171484557906616</v>
       </c>
       <c r="F144" t="n">
         <v>6.35</v>
       </c>
       <c r="G144" t="n">
-        <v>76.23</v>
+        <v>76.19</v>
       </c>
       <c r="H144" t="n">
-        <v>1353.51</v>
+        <v>1352.35</v>
       </c>
       <c r="I144" t="s">
         <v>13</v>
@@ -6057,16 +6057,16 @@
         <v>167</v>
       </c>
       <c r="E145" t="n">
-        <v>0.131012690540147</v>
+        <v>0.131051712661375</v>
       </c>
       <c r="F145" t="n">
         <v>8.14</v>
       </c>
       <c r="G145" t="n">
-        <v>127.09</v>
+        <v>127.02</v>
       </c>
       <c r="H145" t="n">
-        <v>2942.69</v>
+        <v>2940.14</v>
       </c>
       <c r="I145" t="s">
         <v>13</v>
@@ -6089,7 +6089,7 @@
         <v>170</v>
       </c>
       <c r="E146" t="n">
-        <v>1.51744091022657</v>
+        <v>1.51747698763049</v>
       </c>
       <c r="F146" t="n">
         <v>1.28</v>
@@ -6121,7 +6121,7 @@
         <v>171</v>
       </c>
       <c r="E147" t="n">
-        <v>0.986414120842694</v>
+        <v>0.98632941573758</v>
       </c>
       <c r="F147" t="n">
         <v>1.59</v>
@@ -6153,7 +6153,7 @@
         <v>172</v>
       </c>
       <c r="E148" t="n">
-        <v>0.838116944219314</v>
+        <v>0.837946278882307</v>
       </c>
       <c r="F148" t="n">
         <v>1.76</v>
@@ -6162,7 +6162,7 @@
         <v>4.88</v>
       </c>
       <c r="H148" t="n">
-        <v>18.85</v>
+        <v>18.86</v>
       </c>
       <c r="I148" t="s">
         <v>13</v>
@@ -6185,7 +6185,7 @@
         <v>173</v>
       </c>
       <c r="E149" t="n">
-        <v>0.728364812091525</v>
+        <v>0.728503002618658</v>
       </c>
       <c r="F149" t="n">
         <v>1.93</v>
@@ -6194,7 +6194,7 @@
         <v>6.03</v>
       </c>
       <c r="H149" t="n">
-        <v>26.54</v>
+        <v>26.52</v>
       </c>
       <c r="I149" t="s">
         <v>13</v>
@@ -6217,7 +6217,7 @@
         <v>174</v>
       </c>
       <c r="E150" t="n">
-        <v>0.718121447436495</v>
+        <v>0.717964018453761</v>
       </c>
       <c r="F150" t="n">
         <v>1.95</v>
@@ -6226,7 +6226,7 @@
         <v>6.17</v>
       </c>
       <c r="H150" t="n">
-        <v>27.49</v>
+        <v>27.5</v>
       </c>
       <c r="I150" t="s">
         <v>13</v>
@@ -6249,7 +6249,7 @@
         <v>175</v>
       </c>
       <c r="E151" t="n">
-        <v>0.703696616218723</v>
+        <v>0.703389137346057</v>
       </c>
       <c r="F151" t="n">
         <v>1.98</v>
@@ -6258,7 +6258,7 @@
         <v>6.37</v>
       </c>
       <c r="H151" t="n">
-        <v>28.91</v>
+        <v>28.94</v>
       </c>
       <c r="I151" t="s">
         <v>13</v>
@@ -6281,7 +6281,7 @@
         <v>176</v>
       </c>
       <c r="E152" t="n">
-        <v>0.680562530239794</v>
+        <v>0.680267546760492</v>
       </c>
       <c r="F152" t="n">
         <v>2.03</v>
@@ -6290,7 +6290,7 @@
         <v>6.71</v>
       </c>
       <c r="H152" t="n">
-        <v>31.43</v>
+        <v>31.46</v>
       </c>
       <c r="I152" t="s">
         <v>13</v>
@@ -6313,7 +6313,7 @@
         <v>177</v>
       </c>
       <c r="E153" t="n">
-        <v>0.602437325173111</v>
+        <v>0.60228083032565</v>
       </c>
       <c r="F153" t="n">
         <v>2.21</v>
@@ -6322,7 +6322,7 @@
         <v>8.15</v>
       </c>
       <c r="H153" t="n">
-        <v>42.81</v>
+        <v>42.84</v>
       </c>
       <c r="I153" t="s">
         <v>13</v>
@@ -6345,16 +6345,16 @@
         <v>178</v>
       </c>
       <c r="E154" t="n">
-        <v>0.581822602784851</v>
+        <v>0.581526122854658</v>
       </c>
       <c r="F154" t="n">
         <v>2.27</v>
       </c>
       <c r="G154" t="n">
-        <v>8.62</v>
+        <v>8.63</v>
       </c>
       <c r="H154" t="n">
-        <v>46.82</v>
+        <v>46.88</v>
       </c>
       <c r="I154" t="s">
         <v>13</v>
@@ -6377,16 +6377,16 @@
         <v>179</v>
       </c>
       <c r="E155" t="n">
-        <v>0.406266336841939</v>
+        <v>0.406063207204931</v>
       </c>
       <c r="F155" t="n">
         <v>3</v>
       </c>
       <c r="G155" t="n">
-        <v>15.81</v>
+        <v>15.83</v>
       </c>
       <c r="H155" t="n">
-        <v>120.97</v>
+        <v>121.13</v>
       </c>
       <c r="I155" t="s">
         <v>13</v>
@@ -6409,7 +6409,7 @@
         <v>180</v>
       </c>
       <c r="E156" t="n">
-        <v>0.306587109321969</v>
+        <v>0.30663803997396</v>
       </c>
       <c r="F156" t="n">
         <v>3.79</v>
@@ -6418,7 +6418,7 @@
         <v>26.03</v>
       </c>
       <c r="H156" t="n">
-        <v>261.56</v>
+        <v>261.44</v>
       </c>
       <c r="I156" t="s">
         <v>13</v>
@@ -6441,16 +6441,16 @@
         <v>181</v>
       </c>
       <c r="E157" t="n">
-        <v>0.284142250348982</v>
+        <v>0.284189452431615</v>
       </c>
       <c r="F157" t="n">
         <v>4.04</v>
       </c>
       <c r="G157" t="n">
-        <v>29.87</v>
+        <v>29.86</v>
       </c>
       <c r="H157" t="n">
-        <v>323.17</v>
+        <v>323.02</v>
       </c>
       <c r="I157" t="s">
         <v>13</v>
@@ -6473,16 +6473,16 @@
         <v>182</v>
       </c>
       <c r="E158" t="n">
-        <v>0.269298863473827</v>
+        <v>0.2693435997536</v>
       </c>
       <c r="F158" t="n">
         <v>4.24</v>
       </c>
       <c r="G158" t="n">
-        <v>32.93</v>
+        <v>32.92</v>
       </c>
       <c r="H158" t="n">
-        <v>375.46</v>
+        <v>375.29</v>
       </c>
       <c r="I158" t="s">
         <v>13</v>
@@ -6505,16 +6505,16 @@
         <v>183</v>
       </c>
       <c r="E159" t="n">
-        <v>0.252460966230495</v>
+        <v>0.252518483691506</v>
       </c>
       <c r="F159" t="n">
         <v>4.48</v>
       </c>
       <c r="G159" t="n">
-        <v>37.06</v>
+        <v>37.05</v>
       </c>
       <c r="H159" t="n">
-        <v>450.06</v>
+        <v>449.78</v>
       </c>
       <c r="I159" t="s">
         <v>13</v>
@@ -6537,16 +6537,16 @@
         <v>184</v>
       </c>
       <c r="E160" t="n">
-        <v>0.188030362265354</v>
+        <v>0.18807746188024</v>
       </c>
       <c r="F160" t="n">
         <v>5.83</v>
       </c>
       <c r="G160" t="n">
-        <v>64.06</v>
+        <v>64.03</v>
       </c>
       <c r="H160" t="n">
-        <v>1038.54</v>
+        <v>1037.79</v>
       </c>
       <c r="I160" t="s">
         <v>13</v>
@@ -6569,16 +6569,16 @@
         <v>185</v>
       </c>
       <c r="E161" t="n">
-        <v>0.156389706407292</v>
+        <v>0.156415686070069</v>
       </c>
       <c r="F161" t="n">
         <v>6.91</v>
       </c>
       <c r="G161" t="n">
-        <v>90.7</v>
+        <v>90.67</v>
       </c>
       <c r="H161" t="n">
-        <v>1763.05</v>
+        <v>1762.21</v>
       </c>
       <c r="I161" t="s">
         <v>13</v>
@@ -6601,16 +6601,16 @@
         <v>186</v>
       </c>
       <c r="E162" t="n">
-        <v>0.155687206228101</v>
+        <v>0.155728040068052</v>
       </c>
       <c r="F162" t="n">
-        <v>6.94</v>
+        <v>6.93</v>
       </c>
       <c r="G162" t="n">
-        <v>91.48</v>
+        <v>91.43</v>
       </c>
       <c r="H162" t="n">
-        <v>1786.09</v>
+        <v>1784.74</v>
       </c>
       <c r="I162" t="s">
         <v>13</v>
@@ -6633,16 +6633,16 @@
         <v>187</v>
       </c>
       <c r="E163" t="n">
-        <v>0.0926609947217127</v>
+        <v>0.0926763876874697</v>
       </c>
       <c r="F163" t="n">
         <v>11.3</v>
       </c>
       <c r="G163" t="n">
-        <v>247.72</v>
+        <v>247.64</v>
       </c>
       <c r="H163" t="n">
-        <v>8082.98</v>
+        <v>8079.05</v>
       </c>
       <c r="I163" t="s">
         <v>13</v>
@@ -6665,7 +6665,7 @@
         <v>189</v>
       </c>
       <c r="E164" t="n">
-        <v>2.25852778401473</v>
+        <v>2.25889173093496</v>
       </c>
       <c r="F164" t="n">
         <v>1.12</v>
@@ -6697,7 +6697,7 @@
         <v>190</v>
       </c>
       <c r="E165" t="n">
-        <v>1.56459765882402</v>
+        <v>1.56469906189508</v>
       </c>
       <c r="F165" t="n">
         <v>1.26</v>
@@ -6729,7 +6729,7 @@
         <v>191</v>
       </c>
       <c r="E166" t="n">
-        <v>1.20507420727449</v>
+        <v>1.20513677922709</v>
       </c>
       <c r="F166" t="n">
         <v>1.43</v>
@@ -6761,7 +6761,7 @@
         <v>192</v>
       </c>
       <c r="E167" t="n">
-        <v>1.20139714120554</v>
+        <v>1.20175698819679</v>
       </c>
       <c r="F167" t="n">
         <v>1.43</v>
@@ -6770,7 +6770,7 @@
         <v>2.96</v>
       </c>
       <c r="H167" t="n">
-        <v>8.28</v>
+        <v>8.27</v>
       </c>
       <c r="I167" t="s">
         <v>13</v>
@@ -6793,7 +6793,7 @@
         <v>193</v>
       </c>
       <c r="E168" t="n">
-        <v>1.05005802036278</v>
+        <v>1.05007654399624</v>
       </c>
       <c r="F168" t="n">
         <v>1.54</v>
@@ -6825,7 +6825,7 @@
         <v>194</v>
       </c>
       <c r="E169" t="n">
-        <v>1.0373176113907</v>
+        <v>1.03763198891062</v>
       </c>
       <c r="F169" t="n">
         <v>1.55</v>
@@ -6834,7 +6834,7 @@
         <v>3.6</v>
       </c>
       <c r="H169" t="n">
-        <v>11.46</v>
+        <v>11.45</v>
       </c>
       <c r="I169" t="s">
         <v>13</v>
@@ -6857,7 +6857,7 @@
         <v>195</v>
       </c>
       <c r="E170" t="n">
-        <v>0.980672909826364</v>
+        <v>0.980383451296295</v>
       </c>
       <c r="F170" t="n">
         <v>1.6</v>
@@ -6866,7 +6866,7 @@
         <v>3.89</v>
       </c>
       <c r="H170" t="n">
-        <v>13.02</v>
+        <v>13.03</v>
       </c>
       <c r="I170" t="s">
         <v>13</v>
@@ -6889,7 +6889,7 @@
         <v>196</v>
       </c>
       <c r="E171" t="n">
-        <v>0.901128831431512</v>
+        <v>0.901060078574029</v>
       </c>
       <c r="F171" t="n">
         <v>1.68</v>
@@ -6898,7 +6898,7 @@
         <v>4.39</v>
       </c>
       <c r="H171" t="n">
-        <v>15.86</v>
+        <v>15.87</v>
       </c>
       <c r="I171" t="s">
         <v>13</v>
@@ -6921,7 +6921,7 @@
         <v>197</v>
       </c>
       <c r="E172" t="n">
-        <v>0.778883546070897</v>
+        <v>0.778744834491832</v>
       </c>
       <c r="F172" t="n">
         <v>1.85</v>
@@ -6930,7 +6930,7 @@
         <v>5.45</v>
       </c>
       <c r="H172" t="n">
-        <v>22.5</v>
+        <v>22.51</v>
       </c>
       <c r="I172" t="s">
         <v>13</v>
@@ -6953,7 +6953,7 @@
         <v>198</v>
       </c>
       <c r="E173" t="n">
-        <v>0.774399451336263</v>
+        <v>0.774265851620471</v>
       </c>
       <c r="F173" t="n">
         <v>1.86</v>
@@ -6962,7 +6962,7 @@
         <v>5.49</v>
       </c>
       <c r="H173" t="n">
-        <v>22.82</v>
+        <v>22.83</v>
       </c>
       <c r="I173" t="s">
         <v>13</v>
@@ -6985,7 +6985,7 @@
         <v>199</v>
       </c>
       <c r="E174" t="n">
-        <v>0.649468157677254</v>
+        <v>0.649391932351337</v>
       </c>
       <c r="F174" t="n">
         <v>2.09</v>
@@ -6994,7 +6994,7 @@
         <v>7.22</v>
       </c>
       <c r="H174" t="n">
-        <v>35.36</v>
+        <v>35.37</v>
       </c>
       <c r="I174" t="s">
         <v>13</v>
@@ -7017,16 +7017,16 @@
         <v>200</v>
       </c>
       <c r="E175" t="n">
-        <v>0.627377743548761</v>
+        <v>0.627302098835957</v>
       </c>
       <c r="F175" t="n">
         <v>2.15</v>
       </c>
       <c r="G175" t="n">
-        <v>7.63</v>
+        <v>7.64</v>
       </c>
       <c r="H175" t="n">
-        <v>38.6</v>
+        <v>38.61</v>
       </c>
       <c r="I175" t="s">
         <v>13</v>
@@ -7049,7 +7049,7 @@
         <v>201</v>
       </c>
       <c r="E176" t="n">
-        <v>0.406697355344781</v>
+        <v>0.406812530945988</v>
       </c>
       <c r="F176" t="n">
         <v>2.99</v>
@@ -7058,7 +7058,7 @@
         <v>15.78</v>
       </c>
       <c r="H176" t="n">
-        <v>120.62</v>
+        <v>120.53</v>
       </c>
       <c r="I176" t="s">
         <v>13</v>
@@ -7081,16 +7081,16 @@
         <v>202</v>
       </c>
       <c r="E177" t="n">
-        <v>0.373059755914133</v>
+        <v>0.373186455947682</v>
       </c>
       <c r="F177" t="n">
         <v>3.21</v>
       </c>
       <c r="G177" t="n">
-        <v>18.36</v>
+        <v>18.35</v>
       </c>
       <c r="H177" t="n">
-        <v>152.47</v>
+        <v>152.32</v>
       </c>
       <c r="I177" t="s">
         <v>13</v>
@@ -7113,16 +7113,16 @@
         <v>203</v>
       </c>
       <c r="E178" t="n">
-        <v>0.345812424677558</v>
+        <v>0.345941860630204</v>
       </c>
       <c r="F178" t="n">
         <v>3.42</v>
       </c>
       <c r="G178" t="n">
-        <v>20.99</v>
+        <v>20.98</v>
       </c>
       <c r="H178" t="n">
-        <v>187.62</v>
+        <v>187.43</v>
       </c>
       <c r="I178" t="s">
         <v>13</v>
@@ -7145,16 +7145,16 @@
         <v>204</v>
       </c>
       <c r="E179" t="n">
-        <v>0.243972720416537</v>
+        <v>0.244041812837186</v>
       </c>
       <c r="F179" t="n">
         <v>4.62</v>
       </c>
       <c r="G179" t="n">
-        <v>39.47</v>
+        <v>39.45</v>
       </c>
       <c r="H179" t="n">
-        <v>495.57</v>
+        <v>495.17</v>
       </c>
       <c r="I179" t="s">
         <v>13</v>
@@ -7177,16 +7177,16 @@
         <v>205</v>
       </c>
       <c r="E180" t="n">
-        <v>0.230521346002376</v>
+        <v>0.23061263784941</v>
       </c>
       <c r="F180" t="n">
         <v>4.86</v>
       </c>
       <c r="G180" t="n">
-        <v>43.82</v>
+        <v>43.79</v>
       </c>
       <c r="H180" t="n">
-        <v>581.65</v>
+        <v>581</v>
       </c>
       <c r="I180" t="s">
         <v>13</v>
@@ -7209,16 +7209,16 @@
         <v>206</v>
       </c>
       <c r="E181" t="n">
-        <v>0.118310303854572</v>
+        <v>0.118343809015587</v>
       </c>
       <c r="F181" t="n">
         <v>8.96</v>
       </c>
       <c r="G181" t="n">
-        <v>154.55</v>
+        <v>154.47</v>
       </c>
       <c r="H181" t="n">
-        <v>3958.27</v>
+        <v>3955</v>
       </c>
       <c r="I181" t="s">
         <v>13</v>
@@ -7241,16 +7241,16 @@
         <v>209</v>
       </c>
       <c r="E182" t="n">
-        <v>1.87188331214429</v>
+        <v>1.82274237382965</v>
       </c>
       <c r="F182" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="G182" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="H182" t="n">
-        <v>3.46</v>
+        <v>3.63</v>
       </c>
       <c r="I182" t="s">
         <v>13</v>
@@ -7273,16 +7273,16 @@
         <v>210</v>
       </c>
       <c r="E183" t="n">
-        <v>1.84655800428775</v>
+        <v>1.79809239918914</v>
       </c>
       <c r="F183" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="G183" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="H183" t="n">
-        <v>3.55</v>
+        <v>3.72</v>
       </c>
       <c r="I183" t="s">
         <v>13</v>
@@ -7305,16 +7305,16 @@
         <v>211</v>
       </c>
       <c r="E184" t="n">
-        <v>1.68579727221511</v>
+        <v>1.6415204802307</v>
       </c>
       <c r="F184" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="G184" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="H184" t="n">
-        <v>4.18</v>
+        <v>4.4</v>
       </c>
       <c r="I184" t="s">
         <v>13</v>
@@ -7337,16 +7337,16 @@
         <v>212</v>
       </c>
       <c r="E185" t="n">
-        <v>1.46057716284844</v>
+        <v>1.42221214036743</v>
       </c>
       <c r="F185" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="G185" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="H185" t="n">
-        <v>5.51</v>
+        <v>5.82</v>
       </c>
       <c r="I185" t="s">
         <v>13</v>
@@ -7369,16 +7369,16 @@
         <v>213</v>
       </c>
       <c r="E186" t="n">
-        <v>1.14492505481272</v>
+        <v>1.1150885676263</v>
       </c>
       <c r="F186" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G186" t="n">
-        <v>3.15</v>
+        <v>3.26</v>
       </c>
       <c r="H186" t="n">
-        <v>9.19</v>
+        <v>9.74</v>
       </c>
       <c r="I186" t="s">
         <v>13</v>
@@ -7401,16 +7401,16 @@
         <v>214</v>
       </c>
       <c r="E187" t="n">
-        <v>0.864171818310073</v>
+        <v>0.841137661270201</v>
       </c>
       <c r="F187" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="G187" t="n">
-        <v>4.66</v>
+        <v>4.85</v>
       </c>
       <c r="H187" t="n">
-        <v>17.52</v>
+        <v>18.69</v>
       </c>
       <c r="I187" t="s">
         <v>13</v>
@@ -7433,16 +7433,16 @@
         <v>215</v>
       </c>
       <c r="E188" t="n">
-        <v>0.83405414512586</v>
+        <v>0.812033512496693</v>
       </c>
       <c r="F188" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="G188" t="n">
-        <v>4.91</v>
+        <v>5.11</v>
       </c>
       <c r="H188" t="n">
-        <v>19.07</v>
+        <v>20.34</v>
       </c>
       <c r="I188" t="s">
         <v>13</v>
@@ -7465,16 +7465,16 @@
         <v>216</v>
       </c>
       <c r="E189" t="n">
-        <v>0.807341044675105</v>
+        <v>0.785925002966697</v>
       </c>
       <c r="F189" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="G189" t="n">
-        <v>5.16</v>
+        <v>5.37</v>
       </c>
       <c r="H189" t="n">
-        <v>20.63</v>
+        <v>22.02</v>
       </c>
       <c r="I189" t="s">
         <v>13</v>
@@ -7497,16 +7497,16 @@
         <v>217</v>
       </c>
       <c r="E190" t="n">
-        <v>0.794697539251242</v>
+        <v>0.773992700266436</v>
       </c>
       <c r="F190" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="G190" t="n">
-        <v>5.28</v>
+        <v>5.5</v>
       </c>
       <c r="H190" t="n">
-        <v>21.43</v>
+        <v>22.85</v>
       </c>
       <c r="I190" t="s">
         <v>13</v>
@@ -7529,16 +7529,16 @@
         <v>218</v>
       </c>
       <c r="E191" t="n">
-        <v>0.753258023579352</v>
+        <v>0.733330286497361</v>
       </c>
       <c r="F191" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="G191" t="n">
-        <v>5.73</v>
+        <v>5.97</v>
       </c>
       <c r="H191" t="n">
-        <v>24.43</v>
+        <v>26.09</v>
       </c>
       <c r="I191" t="s">
         <v>13</v>
@@ -7561,16 +7561,16 @@
         <v>219</v>
       </c>
       <c r="E192" t="n">
-        <v>0.476669724329591</v>
+        <v>0.46423792502069</v>
       </c>
       <c r="F192" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="G192" t="n">
-        <v>12.02</v>
+        <v>12.57</v>
       </c>
       <c r="H192" t="n">
-        <v>78.86</v>
+        <v>84.59</v>
       </c>
       <c r="I192" t="s">
         <v>13</v>
@@ -7593,16 +7593,16 @@
         <v>220</v>
       </c>
       <c r="E193" t="n">
-        <v>0.401265031806919</v>
+        <v>0.390828026726073</v>
       </c>
       <c r="F193" t="n">
-        <v>3.03</v>
+        <v>3.09</v>
       </c>
       <c r="G193" t="n">
-        <v>16.16</v>
+        <v>16.92</v>
       </c>
       <c r="H193" t="n">
-        <v>125.09</v>
+        <v>134.35</v>
       </c>
       <c r="I193" t="s">
         <v>13</v>
@@ -7625,16 +7625,16 @@
         <v>221</v>
       </c>
       <c r="E194" t="n">
-        <v>0.395217013599971</v>
+        <v>0.384933787090532</v>
       </c>
       <c r="F194" t="n">
-        <v>3.06</v>
+        <v>3.13</v>
       </c>
       <c r="G194" t="n">
-        <v>16.59</v>
+        <v>17.37</v>
       </c>
       <c r="H194" t="n">
-        <v>130.34</v>
+        <v>140</v>
       </c>
       <c r="I194" t="s">
         <v>13</v>
@@ -7657,16 +7657,16 @@
         <v>222</v>
       </c>
       <c r="E195" t="n">
-        <v>0.394737136163623</v>
+        <v>0.384442182223642</v>
       </c>
       <c r="F195" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="G195" t="n">
-        <v>16.63</v>
+        <v>17.41</v>
       </c>
       <c r="H195" t="n">
-        <v>130.77</v>
+        <v>140.49</v>
       </c>
       <c r="I195" t="s">
         <v>13</v>
@@ -7689,16 +7689,16 @@
         <v>223</v>
       </c>
       <c r="E196" t="n">
-        <v>0.3736535104353</v>
+        <v>0.363929117157517</v>
       </c>
       <c r="F196" t="n">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="G196" t="n">
-        <v>18.3</v>
+        <v>19.18</v>
       </c>
       <c r="H196" t="n">
-        <v>151.81</v>
+        <v>163.13</v>
       </c>
       <c r="I196" t="s">
         <v>13</v>
@@ -7721,16 +7721,16 @@
         <v>224</v>
       </c>
       <c r="E197" t="n">
-        <v>0.274754214402637</v>
+        <v>0.26761082932093</v>
       </c>
       <c r="F197" t="n">
-        <v>4.16</v>
+        <v>4.26</v>
       </c>
       <c r="G197" t="n">
-        <v>31.75</v>
+        <v>33.31</v>
       </c>
       <c r="H197" t="n">
-        <v>354.97</v>
+        <v>382.13</v>
       </c>
       <c r="I197" t="s">
         <v>13</v>
@@ -7753,16 +7753,16 @@
         <v>225</v>
       </c>
       <c r="E198" t="n">
-        <v>0.188120489168761</v>
+        <v>0.183214207003415</v>
       </c>
       <c r="F198" t="n">
-        <v>5.83</v>
+        <v>5.97</v>
       </c>
       <c r="G198" t="n">
-        <v>64</v>
+        <v>67.26</v>
       </c>
       <c r="H198" t="n">
-        <v>1037.11</v>
+        <v>1118.6</v>
       </c>
       <c r="I198" t="s">
         <v>13</v>
@@ -7785,16 +7785,16 @@
         <v>226</v>
       </c>
       <c r="E199" t="n">
-        <v>0.148309131073059</v>
+        <v>0.144441150248871</v>
       </c>
       <c r="F199" t="n">
-        <v>7.26</v>
+        <v>7.44</v>
       </c>
       <c r="G199" t="n">
-        <v>100.32</v>
+        <v>105.49</v>
       </c>
       <c r="H199" t="n">
-        <v>2054.82</v>
+        <v>2217.96</v>
       </c>
       <c r="I199" t="s">
         <v>13</v>
@@ -7817,16 +7817,16 @@
         <v>228</v>
       </c>
       <c r="E200" t="n">
-        <v>1.11571406420128</v>
+        <v>1.06052068635221</v>
       </c>
       <c r="F200" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="G200" t="n">
-        <v>3.26</v>
+        <v>3.49</v>
       </c>
       <c r="H200" t="n">
-        <v>9.73</v>
+        <v>10.9</v>
       </c>
       <c r="I200" t="s">
         <v>13</v>
@@ -7849,16 +7849,16 @@
         <v>229</v>
       </c>
       <c r="E201" t="n">
-        <v>0.802631381377793</v>
+        <v>0.762827260291856</v>
       </c>
       <c r="F201" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="G201" t="n">
-        <v>5.2</v>
+        <v>5.62</v>
       </c>
       <c r="H201" t="n">
-        <v>20.92</v>
+        <v>23.68</v>
       </c>
       <c r="I201" t="s">
         <v>13</v>
@@ -7881,16 +7881,16 @@
         <v>230</v>
       </c>
       <c r="E202" t="n">
-        <v>0.778279328254448</v>
+        <v>0.73970729168369</v>
       </c>
       <c r="F202" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="G202" t="n">
-        <v>5.45</v>
+        <v>5.89</v>
       </c>
       <c r="H202" t="n">
-        <v>22.55</v>
+        <v>25.54</v>
       </c>
       <c r="I202" t="s">
         <v>13</v>
@@ -7913,16 +7913,16 @@
         <v>231</v>
       </c>
       <c r="E203" t="n">
-        <v>0.706070861764507</v>
+        <v>0.671095058535639</v>
       </c>
       <c r="F203" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="G203" t="n">
-        <v>6.33</v>
+        <v>6.86</v>
       </c>
       <c r="H203" t="n">
-        <v>28.67</v>
+        <v>32.55</v>
       </c>
       <c r="I203" t="s">
         <v>13</v>
@@ -7945,16 +7945,16 @@
         <v>232</v>
       </c>
       <c r="E204" t="n">
-        <v>0.646317727638378</v>
+        <v>0.614324579763168</v>
       </c>
       <c r="F204" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="G204" t="n">
-        <v>7.28</v>
+        <v>7.9</v>
       </c>
       <c r="H204" t="n">
-        <v>35.79</v>
+        <v>40.73</v>
       </c>
       <c r="I204" t="s">
         <v>13</v>
@@ -7977,16 +7977,16 @@
         <v>233</v>
       </c>
       <c r="E205" t="n">
-        <v>0.608685504361324</v>
+        <v>0.578306630249859</v>
       </c>
       <c r="F205" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="G205" t="n">
-        <v>8.01</v>
+        <v>8.71</v>
       </c>
       <c r="H205" t="n">
-        <v>41.7</v>
+        <v>47.56</v>
       </c>
       <c r="I205" t="s">
         <v>13</v>
@@ -8009,16 +8009,16 @@
         <v>234</v>
       </c>
       <c r="E206" t="n">
-        <v>0.521170947423356</v>
+        <v>0.495187313396116</v>
       </c>
       <c r="F206" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="G206" t="n">
-        <v>10.34</v>
+        <v>11.27</v>
       </c>
       <c r="H206" t="n">
-        <v>62.33</v>
+        <v>71.3</v>
       </c>
       <c r="I206" t="s">
         <v>13</v>
@@ -8041,16 +8041,16 @@
         <v>235</v>
       </c>
       <c r="E207" t="n">
-        <v>0.458900255994113</v>
+        <v>0.436331209867079</v>
       </c>
       <c r="F207" t="n">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="G207" t="n">
-        <v>12.82</v>
+        <v>13.98</v>
       </c>
       <c r="H207" t="n">
-        <v>87.24</v>
+        <v>99.82</v>
       </c>
       <c r="I207" t="s">
         <v>13</v>
@@ -8073,16 +8073,16 @@
         <v>236</v>
       </c>
       <c r="E208" t="n">
-        <v>0.446106155230075</v>
+        <v>0.423918935406381</v>
       </c>
       <c r="F208" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="G208" t="n">
-        <v>13.45</v>
+        <v>14.69</v>
       </c>
       <c r="H208" t="n">
-        <v>94.08</v>
+        <v>107.87</v>
       </c>
       <c r="I208" t="s">
         <v>13</v>
@@ -8105,16 +8105,16 @@
         <v>237</v>
       </c>
       <c r="E209" t="n">
-        <v>0.330011618100516</v>
+        <v>0.313793568140797</v>
       </c>
       <c r="F209" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="G209" t="n">
-        <v>22.81</v>
+        <v>24.97</v>
       </c>
       <c r="H209" t="n">
-        <v>213.38</v>
+        <v>245.25</v>
       </c>
       <c r="I209" t="s">
         <v>13</v>
@@ -8137,16 +8137,16 @@
         <v>238</v>
       </c>
       <c r="E210" t="n">
-        <v>0.304971768103421</v>
+        <v>0.289983039174591</v>
       </c>
       <c r="F210" t="n">
-        <v>3.8</v>
+        <v>3.97</v>
       </c>
       <c r="G210" t="n">
-        <v>26.28</v>
+        <v>28.79</v>
       </c>
       <c r="H210" t="n">
-        <v>265.42</v>
+        <v>305.35</v>
       </c>
       <c r="I210" t="s">
         <v>13</v>
@@ -8169,16 +8169,16 @@
         <v>239</v>
       </c>
       <c r="E211" t="n">
-        <v>0.224956519277455</v>
+        <v>0.213885508714529</v>
       </c>
       <c r="F211" t="n">
-        <v>4.96</v>
+        <v>5.19</v>
       </c>
       <c r="G211" t="n">
-        <v>45.85</v>
+        <v>50.35</v>
       </c>
       <c r="H211" t="n">
-        <v>623.32</v>
+        <v>719.28</v>
       </c>
       <c r="I211" t="s">
         <v>13</v>
@@ -8201,16 +8201,16 @@
         <v>240</v>
       </c>
       <c r="E212" t="n">
-        <v>0.202854884966046</v>
+        <v>0.192889039628308</v>
       </c>
       <c r="F212" t="n">
-        <v>5.45</v>
+        <v>5.7</v>
       </c>
       <c r="G212" t="n">
-        <v>55.58</v>
+        <v>61.07</v>
       </c>
       <c r="H212" t="n">
-        <v>836.24</v>
+        <v>965.5</v>
       </c>
       <c r="I212" t="s">
         <v>13</v>
@@ -8233,16 +8233,16 @@
         <v>241</v>
       </c>
       <c r="E213" t="n">
-        <v>0.202185696750794</v>
+        <v>0.192249361917094</v>
       </c>
       <c r="F213" t="n">
-        <v>5.46</v>
+        <v>5.72</v>
       </c>
       <c r="G213" t="n">
-        <v>55.92</v>
+        <v>61.45</v>
       </c>
       <c r="H213" t="n">
-        <v>844.15</v>
+        <v>974.7</v>
       </c>
       <c r="I213" t="s">
         <v>13</v>
@@ -8265,16 +8265,16 @@
         <v>242</v>
       </c>
       <c r="E214" t="n">
-        <v>0.196751255059372</v>
+        <v>0.187093723500665</v>
       </c>
       <c r="F214" t="n">
-        <v>5.6</v>
+        <v>5.86</v>
       </c>
       <c r="G214" t="n">
-        <v>58.84</v>
+        <v>64.66</v>
       </c>
       <c r="H214" t="n">
-        <v>912.36</v>
+        <v>1053.48</v>
       </c>
       <c r="I214" t="s">
         <v>13</v>
@@ -8297,16 +8297,16 @@
         <v>243</v>
       </c>
       <c r="E215" t="n">
-        <v>0.112307116996619</v>
+        <v>0.106780034329466</v>
       </c>
       <c r="F215" t="n">
-        <v>9.41</v>
+        <v>9.87</v>
       </c>
       <c r="G215" t="n">
-        <v>170.84</v>
+        <v>188.29</v>
       </c>
       <c r="H215" t="n">
-        <v>4606.88</v>
+        <v>5337.87</v>
       </c>
       <c r="I215" t="s">
         <v>13</v>
@@ -8329,16 +8329,16 @@
         <v>244</v>
       </c>
       <c r="E216" t="n">
-        <v>0.105272459258624</v>
+        <v>0.100091580250623</v>
       </c>
       <c r="F216" t="n">
-        <v>10.01</v>
+        <v>10.5</v>
       </c>
       <c r="G216" t="n">
-        <v>193.53</v>
+        <v>213.35</v>
       </c>
       <c r="H216" t="n">
-        <v>5564.24</v>
+        <v>6448.79</v>
       </c>
       <c r="I216" t="s">
         <v>13</v>
@@ -8361,16 +8361,16 @@
         <v>245</v>
       </c>
       <c r="E217" t="n">
-        <v>0.0864785349928449</v>
+        <v>0.082222580209017</v>
       </c>
       <c r="F217" t="n">
-        <v>12.07</v>
+        <v>12.67</v>
       </c>
       <c r="G217" t="n">
-        <v>283.24</v>
+        <v>312.44</v>
       </c>
       <c r="H217" t="n">
-        <v>9897.67</v>
+        <v>11479.01</v>
       </c>
       <c r="I217" t="s">
         <v>13</v>
@@ -8393,7 +8393,7 @@
         <v>248</v>
       </c>
       <c r="E218" t="n">
-        <v>1.39178587045991</v>
+        <v>1.39165944768275</v>
       </c>
       <c r="F218" t="n">
         <v>1.33</v>
@@ -8425,7 +8425,7 @@
         <v>249</v>
       </c>
       <c r="E219" t="n">
-        <v>1.38398494406667</v>
+        <v>1.38394112270128</v>
       </c>
       <c r="F219" t="n">
         <v>1.33</v>
@@ -8457,7 +8457,7 @@
         <v>250</v>
       </c>
       <c r="E220" t="n">
-        <v>1.2000750065408</v>
+        <v>1.20000182558524</v>
       </c>
       <c r="F220" t="n">
         <v>1.43</v>
@@ -8489,7 +8489,7 @@
         <v>251</v>
       </c>
       <c r="E221" t="n">
-        <v>1.19845736273962</v>
+        <v>1.19836210348443</v>
       </c>
       <c r="F221" t="n">
         <v>1.43</v>
@@ -8521,7 +8521,7 @@
         <v>252</v>
       </c>
       <c r="E222" t="n">
-        <v>1.16386487511706</v>
+        <v>1.16369413512509</v>
       </c>
       <c r="F222" t="n">
         <v>1.45</v>
@@ -8553,7 +8553,7 @@
         <v>253</v>
       </c>
       <c r="E223" t="n">
-        <v>1.13234590562404</v>
+        <v>1.13206034644876</v>
       </c>
       <c r="F223" t="n">
         <v>1.48</v>
@@ -8585,7 +8585,7 @@
         <v>254</v>
       </c>
       <c r="E224" t="n">
-        <v>0.896947963823367</v>
+        <v>0.896665099091647</v>
       </c>
       <c r="F224" t="n">
         <v>1.69</v>
@@ -8594,7 +8594,7 @@
         <v>4.42</v>
       </c>
       <c r="H224" t="n">
-        <v>16.04</v>
+        <v>16.05</v>
       </c>
       <c r="I224" t="s">
         <v>13</v>
@@ -8617,16 +8617,16 @@
         <v>255</v>
       </c>
       <c r="E225" t="n">
-        <v>0.652711495200643</v>
+        <v>0.652852293973397</v>
       </c>
       <c r="F225" t="n">
         <v>2.09</v>
       </c>
       <c r="G225" t="n">
-        <v>7.17</v>
+        <v>7.16</v>
       </c>
       <c r="H225" t="n">
-        <v>34.91</v>
+        <v>34.89</v>
       </c>
       <c r="I225" t="s">
         <v>13</v>
@@ -8649,16 +8649,16 @@
         <v>256</v>
       </c>
       <c r="E226" t="n">
-        <v>0.555085073350279</v>
+        <v>0.555209864202175</v>
       </c>
       <c r="F226" t="n">
         <v>2.35</v>
       </c>
       <c r="G226" t="n">
-        <v>9.32</v>
+        <v>9.31</v>
       </c>
       <c r="H226" t="n">
-        <v>52.88</v>
+        <v>52.85</v>
       </c>
       <c r="I226" t="s">
         <v>13</v>
@@ -8681,16 +8681,16 @@
         <v>257</v>
       </c>
       <c r="E227" t="n">
-        <v>0.440863654620004</v>
+        <v>0.440978755197724</v>
       </c>
       <c r="F227" t="n">
         <v>2.8</v>
       </c>
       <c r="G227" t="n">
-        <v>13.73</v>
+        <v>13.72</v>
       </c>
       <c r="H227" t="n">
-        <v>97.1</v>
+        <v>97.03</v>
       </c>
       <c r="I227" t="s">
         <v>13</v>
@@ -8713,7 +8713,7 @@
         <v>258</v>
       </c>
       <c r="E228" t="n">
-        <v>0.426744205089943</v>
+        <v>0.42685223697493</v>
       </c>
       <c r="F228" t="n">
         <v>2.88</v>
@@ -8722,7 +8722,7 @@
         <v>14.52</v>
       </c>
       <c r="H228" t="n">
-        <v>105.96</v>
+        <v>105.88</v>
       </c>
       <c r="I228" t="s">
         <v>13</v>
@@ -8745,7 +8745,7 @@
         <v>259</v>
       </c>
       <c r="E229" t="n">
-        <v>0.401357275027201</v>
+        <v>0.401430457857518</v>
       </c>
       <c r="F229" t="n">
         <v>3.02</v>
@@ -8754,7 +8754,7 @@
         <v>16.15</v>
       </c>
       <c r="H229" t="n">
-        <v>125.01</v>
+        <v>124.95</v>
       </c>
       <c r="I229" t="s">
         <v>13</v>
@@ -8777,16 +8777,16 @@
         <v>260</v>
       </c>
       <c r="E230" t="n">
-        <v>0.382631093620423</v>
+        <v>0.382727613134679</v>
       </c>
       <c r="F230" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="G230" t="n">
-        <v>17.56</v>
+        <v>17.55</v>
       </c>
       <c r="H230" t="n">
-        <v>142.31</v>
+        <v>142.21</v>
       </c>
       <c r="I230" t="s">
         <v>13</v>
@@ -8809,16 +8809,16 @@
         <v>261</v>
       </c>
       <c r="E231" t="n">
-        <v>0.38031162693244</v>
+        <v>0.380404922639787</v>
       </c>
       <c r="F231" t="n">
         <v>3.16</v>
       </c>
       <c r="G231" t="n">
-        <v>17.75</v>
+        <v>17.74</v>
       </c>
       <c r="H231" t="n">
-        <v>144.68</v>
+        <v>144.58</v>
       </c>
       <c r="I231" t="s">
         <v>13</v>
@@ -8841,16 +8841,16 @@
         <v>262</v>
       </c>
       <c r="E232" t="n">
-        <v>0.366577122535529</v>
+        <v>0.366683671844351</v>
       </c>
       <c r="F232" t="n">
         <v>3.26</v>
       </c>
       <c r="G232" t="n">
-        <v>18.93</v>
+        <v>18.92</v>
       </c>
       <c r="H232" t="n">
-        <v>159.93</v>
+        <v>159.81</v>
       </c>
       <c r="I232" t="s">
         <v>13</v>
@@ -8873,16 +8873,16 @@
         <v>263</v>
       </c>
       <c r="E233" t="n">
-        <v>0.189621295028122</v>
+        <v>0.189655870265503</v>
       </c>
       <c r="F233" t="n">
         <v>5.79</v>
       </c>
       <c r="G233" t="n">
-        <v>63.05</v>
+        <v>63.03</v>
       </c>
       <c r="H233" t="n">
-        <v>1013.81</v>
+        <v>1013.28</v>
       </c>
       <c r="I233" t="s">
         <v>13</v>
@@ -8905,16 +8905,16 @@
         <v>264</v>
       </c>
       <c r="E234" t="n">
-        <v>0.162783917691124</v>
+        <v>0.162813599444933</v>
       </c>
       <c r="F234" t="n">
         <v>6.66</v>
       </c>
       <c r="G234" t="n">
-        <v>84.07</v>
+        <v>84.04</v>
       </c>
       <c r="H234" t="n">
-        <v>1570.8</v>
+        <v>1569.98</v>
       </c>
       <c r="I234" t="s">
         <v>13</v>
@@ -8937,16 +8937,16 @@
         <v>265</v>
       </c>
       <c r="E235" t="n">
-        <v>0.11503352645177</v>
+        <v>0.115054501477192</v>
       </c>
       <c r="F235" t="n">
         <v>9.2</v>
       </c>
       <c r="G235" t="n">
-        <v>163.13</v>
+        <v>163.07</v>
       </c>
       <c r="H235" t="n">
-        <v>4295.74</v>
+        <v>4293.46</v>
       </c>
       <c r="I235" t="s">
         <v>13</v>
@@ -8969,7 +8969,7 @@
         <v>267</v>
       </c>
       <c r="E236" t="n">
-        <v>1.35495571114083</v>
+        <v>1.35497479468201</v>
       </c>
       <c r="F236" t="n">
         <v>1.35</v>
@@ -9001,7 +9001,7 @@
         <v>268</v>
       </c>
       <c r="E237" t="n">
-        <v>1.24044322796809</v>
+        <v>1.24039795664472</v>
       </c>
       <c r="F237" t="n">
         <v>1.41</v>
@@ -9033,7 +9033,7 @@
         <v>269</v>
       </c>
       <c r="E238" t="n">
-        <v>1.23493884364109</v>
+        <v>1.23490221635609</v>
       </c>
       <c r="F238" t="n">
         <v>1.41</v>
@@ -9065,7 +9065,7 @@
         <v>270</v>
       </c>
       <c r="E239" t="n">
-        <v>1.13430526661505</v>
+        <v>1.13397608289523</v>
       </c>
       <c r="F239" t="n">
         <v>1.47</v>
@@ -9074,7 +9074,7 @@
         <v>3.19</v>
       </c>
       <c r="H239" t="n">
-        <v>9.38</v>
+        <v>9.39</v>
       </c>
       <c r="I239" t="s">
         <v>13</v>
@@ -9097,7 +9097,7 @@
         <v>271</v>
       </c>
       <c r="E240" t="n">
-        <v>0.912969357884419</v>
+        <v>0.912885904777327</v>
       </c>
       <c r="F240" t="n">
         <v>1.67</v>
@@ -9106,7 +9106,7 @@
         <v>4.31</v>
       </c>
       <c r="H240" t="n">
-        <v>15.38</v>
+        <v>15.39</v>
       </c>
       <c r="I240" t="s">
         <v>13</v>
@@ -9129,7 +9129,7 @@
         <v>272</v>
       </c>
       <c r="E241" t="n">
-        <v>0.903534936214159</v>
+        <v>0.903479861670477</v>
       </c>
       <c r="F241" t="n">
         <v>1.68</v>
@@ -9138,7 +9138,7 @@
         <v>4.37</v>
       </c>
       <c r="H241" t="n">
-        <v>15.76</v>
+        <v>15.77</v>
       </c>
       <c r="I241" t="s">
         <v>13</v>
@@ -9161,7 +9161,7 @@
         <v>273</v>
       </c>
       <c r="E242" t="n">
-        <v>0.765601041983495</v>
+        <v>0.76550339552361</v>
       </c>
       <c r="F242" t="n">
         <v>1.87</v>
@@ -9170,7 +9170,7 @@
         <v>5.59</v>
       </c>
       <c r="H242" t="n">
-        <v>23.47</v>
+        <v>23.48</v>
       </c>
       <c r="I242" t="s">
         <v>13</v>
@@ -9193,7 +9193,7 @@
         <v>274</v>
       </c>
       <c r="E243" t="n">
-        <v>0.639372711747462</v>
+        <v>0.639220904344628</v>
       </c>
       <c r="F243" t="n">
         <v>2.12</v>
@@ -9202,7 +9202,7 @@
         <v>7.41</v>
       </c>
       <c r="H243" t="n">
-        <v>36.79</v>
+        <v>36.81</v>
       </c>
       <c r="I243" t="s">
         <v>13</v>
@@ -9225,7 +9225,7 @@
         <v>275</v>
       </c>
       <c r="E244" t="n">
-        <v>0.580620926580857</v>
+        <v>0.58074883364377</v>
       </c>
       <c r="F244" t="n">
         <v>2.27</v>
@@ -9234,7 +9234,7 @@
         <v>8.65</v>
       </c>
       <c r="H244" t="n">
-        <v>47.07</v>
+        <v>47.04</v>
       </c>
       <c r="I244" t="s">
         <v>13</v>
@@ -9257,7 +9257,7 @@
         <v>276</v>
       </c>
       <c r="E245" t="n">
-        <v>0.510956779537202</v>
+        <v>0.511071047377089</v>
       </c>
       <c r="F245" t="n">
         <v>2.5</v>
@@ -9266,7 +9266,7 @@
         <v>10.69</v>
       </c>
       <c r="H245" t="n">
-        <v>65.65</v>
+        <v>65.61</v>
       </c>
       <c r="I245" t="s">
         <v>13</v>
@@ -9289,7 +9289,7 @@
         <v>277</v>
       </c>
       <c r="E246" t="n">
-        <v>0.443488197101226</v>
+        <v>0.443571997017054</v>
       </c>
       <c r="F246" t="n">
         <v>2.79</v>
@@ -9298,7 +9298,7 @@
         <v>13.59</v>
       </c>
       <c r="H246" t="n">
-        <v>95.57</v>
+        <v>95.52</v>
       </c>
       <c r="I246" t="s">
         <v>13</v>
@@ -9321,16 +9321,16 @@
         <v>278</v>
       </c>
       <c r="E247" t="n">
-        <v>0.431987993560045</v>
+        <v>0.432069620439262</v>
       </c>
       <c r="F247" t="n">
         <v>2.85</v>
       </c>
       <c r="G247" t="n">
-        <v>14.22</v>
+        <v>14.21</v>
       </c>
       <c r="H247" t="n">
-        <v>102.54</v>
+        <v>102.49</v>
       </c>
       <c r="I247" t="s">
         <v>13</v>
@@ -9353,16 +9353,16 @@
         <v>279</v>
       </c>
       <c r="E248" t="n">
-        <v>0.341359330250099</v>
+        <v>0.341444674420034</v>
       </c>
       <c r="F248" t="n">
         <v>3.46</v>
       </c>
       <c r="G248" t="n">
-        <v>21.48</v>
+        <v>21.47</v>
       </c>
       <c r="H248" t="n">
-        <v>194.42</v>
+        <v>194.28</v>
       </c>
       <c r="I248" t="s">
         <v>13</v>
@@ -9385,16 +9385,16 @@
         <v>280</v>
       </c>
       <c r="E249" t="n">
-        <v>0.286794645481699</v>
+        <v>0.286883150735728</v>
       </c>
       <c r="F249" t="n">
         <v>4.01</v>
       </c>
       <c r="G249" t="n">
-        <v>29.37</v>
+        <v>29.35</v>
       </c>
       <c r="H249" t="n">
-        <v>314.9</v>
+        <v>314.63</v>
       </c>
       <c r="I249" t="s">
         <v>13</v>
@@ -9417,16 +9417,16 @@
         <v>281</v>
       </c>
       <c r="E250" t="n">
-        <v>0.257758932116751</v>
+        <v>0.257807637306554</v>
       </c>
       <c r="F250" t="n">
         <v>4.4</v>
       </c>
       <c r="G250" t="n">
-        <v>35.68</v>
+        <v>35.67</v>
       </c>
       <c r="H250" t="n">
-        <v>424.54</v>
+        <v>424.31</v>
       </c>
       <c r="I250" t="s">
         <v>13</v>
@@ -9449,16 +9449,16 @@
         <v>282</v>
       </c>
       <c r="E251" t="n">
-        <v>0.231317318369371</v>
+        <v>0.231383146468013</v>
       </c>
       <c r="F251" t="n">
         <v>4.84</v>
       </c>
       <c r="G251" t="n">
-        <v>43.54</v>
+        <v>43.52</v>
       </c>
       <c r="H251" t="n">
-        <v>576.01</v>
+        <v>575.55</v>
       </c>
       <c r="I251" t="s">
         <v>13</v>
@@ -9481,16 +9481,16 @@
         <v>283</v>
       </c>
       <c r="E252" t="n">
-        <v>0.21749187772284</v>
+        <v>0.21753297419658</v>
       </c>
       <c r="F252" t="n">
         <v>5.12</v>
       </c>
       <c r="G252" t="n">
-        <v>48.81</v>
+        <v>48.8</v>
       </c>
       <c r="H252" t="n">
-        <v>685.92</v>
+        <v>685.55</v>
       </c>
       <c r="I252" t="s">
         <v>13</v>
@@ -9513,16 +9513,16 @@
         <v>284</v>
       </c>
       <c r="E253" t="n">
-        <v>0.203976975716994</v>
+        <v>0.204033974555374</v>
       </c>
       <c r="F253" t="n">
         <v>5.42</v>
       </c>
       <c r="G253" t="n">
-        <v>55.01</v>
+        <v>54.98</v>
       </c>
       <c r="H253" t="n">
-        <v>823.2</v>
+        <v>822.54</v>
       </c>
       <c r="I253" t="s">
         <v>13</v>
@@ -9545,7 +9545,7 @@
         <v>287</v>
       </c>
       <c r="E254" t="n">
-        <v>1.7340013627776</v>
+        <v>1.73422375650945</v>
       </c>
       <c r="F254" t="n">
         <v>1.21</v>
@@ -9577,7 +9577,7 @@
         <v>288</v>
       </c>
       <c r="E255" t="n">
-        <v>1.67152334890554</v>
+        <v>1.67173693547808</v>
       </c>
       <c r="F255" t="n">
         <v>1.23</v>
@@ -9609,7 +9609,7 @@
         <v>289</v>
       </c>
       <c r="E256" t="n">
-        <v>1.38023373450106</v>
+        <v>1.38007585026868</v>
       </c>
       <c r="F256" t="n">
         <v>1.34</v>
@@ -9641,7 +9641,7 @@
         <v>290</v>
       </c>
       <c r="E257" t="n">
-        <v>1.17582047273022</v>
+        <v>1.17584117879704</v>
       </c>
       <c r="F257" t="n">
         <v>1.45</v>
@@ -9673,7 +9673,7 @@
         <v>291</v>
       </c>
       <c r="E258" t="n">
-        <v>1.0586082101338</v>
+        <v>1.05827156762688</v>
       </c>
       <c r="F258" t="n">
         <v>1.53</v>
@@ -9682,7 +9682,7 @@
         <v>3.5</v>
       </c>
       <c r="H258" t="n">
-        <v>10.94</v>
+        <v>10.95</v>
       </c>
       <c r="I258" t="s">
         <v>13</v>
@@ -9705,7 +9705,7 @@
         <v>292</v>
       </c>
       <c r="E259" t="n">
-        <v>1.04627144257617</v>
+        <v>1.04601159160308</v>
       </c>
       <c r="F259" t="n">
         <v>1.54</v>
@@ -9737,16 +9737,16 @@
         <v>293</v>
       </c>
       <c r="E260" t="n">
-        <v>0.929424536477289</v>
+        <v>0.929752955187663</v>
       </c>
       <c r="F260" t="n">
         <v>1.65</v>
       </c>
       <c r="G260" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="H260" t="n">
-        <v>14.75</v>
+        <v>14.74</v>
       </c>
       <c r="I260" t="s">
         <v>13</v>
@@ -9769,7 +9769,7 @@
         <v>294</v>
       </c>
       <c r="E261" t="n">
-        <v>0.854798422272704</v>
+        <v>0.85475947728494</v>
       </c>
       <c r="F261" t="n">
         <v>1.74</v>
@@ -9801,7 +9801,7 @@
         <v>295</v>
       </c>
       <c r="E262" t="n">
-        <v>0.831496760206782</v>
+        <v>0.831467586185376</v>
       </c>
       <c r="F262" t="n">
         <v>1.77</v>
@@ -9833,7 +9833,7 @@
         <v>296</v>
       </c>
       <c r="E263" t="n">
-        <v>0.675189015464421</v>
+        <v>0.675071790747577</v>
       </c>
       <c r="F263" t="n">
         <v>2.04</v>
@@ -9842,7 +9842,7 @@
         <v>6.79</v>
       </c>
       <c r="H263" t="n">
-        <v>32.06</v>
+        <v>32.07</v>
       </c>
       <c r="I263" t="s">
         <v>13</v>
@@ -9865,16 +9865,16 @@
         <v>297</v>
       </c>
       <c r="E264" t="n">
-        <v>0.443382603154824</v>
+        <v>0.443551317495095</v>
       </c>
       <c r="F264" t="n">
         <v>2.79</v>
       </c>
       <c r="G264" t="n">
-        <v>13.6</v>
+        <v>13.59</v>
       </c>
       <c r="H264" t="n">
-        <v>95.63</v>
+        <v>95.53</v>
       </c>
       <c r="I264" t="s">
         <v>13</v>
@@ -9897,16 +9897,16 @@
         <v>298</v>
       </c>
       <c r="E265" t="n">
-        <v>0.403434666323709</v>
+        <v>0.4035873435973</v>
       </c>
       <c r="F265" t="n">
         <v>3.01</v>
       </c>
       <c r="G265" t="n">
-        <v>16.01</v>
+        <v>16</v>
       </c>
       <c r="H265" t="n">
-        <v>123.28</v>
+        <v>123.15</v>
       </c>
       <c r="I265" t="s">
         <v>13</v>
@@ -9929,16 +9929,16 @@
         <v>299</v>
       </c>
       <c r="E266" t="n">
-        <v>0.36536883094604</v>
+        <v>0.36548870577529</v>
       </c>
       <c r="F266" t="n">
         <v>3.27</v>
       </c>
       <c r="G266" t="n">
-        <v>19.04</v>
+        <v>19.03</v>
       </c>
       <c r="H266" t="n">
-        <v>161.38</v>
+        <v>161.24</v>
       </c>
       <c r="I266" t="s">
         <v>13</v>
@@ -9961,16 +9961,16 @@
         <v>300</v>
       </c>
       <c r="E267" t="n">
-        <v>0.362447117176454</v>
+        <v>0.362602411082251</v>
       </c>
       <c r="F267" t="n">
         <v>3.29</v>
       </c>
       <c r="G267" t="n">
-        <v>19.31</v>
+        <v>19.3</v>
       </c>
       <c r="H267" t="n">
-        <v>164.96</v>
+        <v>164.77</v>
       </c>
       <c r="I267" t="s">
         <v>13</v>
@@ -9993,16 +9993,16 @@
         <v>301</v>
       </c>
       <c r="E268" t="n">
-        <v>0.336851414940306</v>
+        <v>0.33698453595401</v>
       </c>
       <c r="F268" t="n">
         <v>3.5</v>
       </c>
       <c r="G268" t="n">
-        <v>21.99</v>
+        <v>21.98</v>
       </c>
       <c r="H268" t="n">
-        <v>201.66</v>
+        <v>201.44</v>
       </c>
       <c r="I268" t="s">
         <v>13</v>
@@ -10025,16 +10025,16 @@
         <v>302</v>
       </c>
       <c r="E269" t="n">
-        <v>0.238192164902952</v>
+        <v>0.238270314002377</v>
       </c>
       <c r="F269" t="n">
         <v>4.72</v>
       </c>
       <c r="G269" t="n">
-        <v>41.25</v>
+        <v>41.23</v>
       </c>
       <c r="H269" t="n">
-        <v>530.26</v>
+        <v>529.76</v>
       </c>
       <c r="I269" t="s">
         <v>13</v>
@@ -10057,16 +10057,16 @@
         <v>303</v>
       </c>
       <c r="E270" t="n">
-        <v>0.183649994309071</v>
+        <v>0.183710248523018</v>
       </c>
       <c r="F270" t="n">
         <v>5.96</v>
       </c>
       <c r="G270" t="n">
-        <v>66.96</v>
+        <v>66.92</v>
       </c>
       <c r="H270" t="n">
-        <v>1111.01</v>
+        <v>1109.97</v>
       </c>
       <c r="I270" t="s">
         <v>13</v>
@@ -10089,16 +10089,16 @@
         <v>304</v>
       </c>
       <c r="E271" t="n">
-        <v>0.133053312574297</v>
+        <v>0.133096966388676</v>
       </c>
       <c r="F271" t="n">
-        <v>8.03</v>
+        <v>8.02</v>
       </c>
       <c r="G271" t="n">
-        <v>123.39</v>
+        <v>123.31</v>
       </c>
       <c r="H271" t="n">
-        <v>2813.63</v>
+        <v>2810.96</v>
       </c>
       <c r="I271" t="s">
         <v>13</v>
@@ -10121,7 +10121,7 @@
         <v>306</v>
       </c>
       <c r="E272" t="n">
-        <v>1.53493929950283</v>
+        <v>1.53486270423377</v>
       </c>
       <c r="F272" t="n">
         <v>1.27</v>
@@ -10153,7 +10153,7 @@
         <v>307</v>
       </c>
       <c r="E273" t="n">
-        <v>1.11767786253117</v>
+        <v>1.11750357510818</v>
       </c>
       <c r="F273" t="n">
         <v>1.49</v>
@@ -10162,7 +10162,7 @@
         <v>3.25</v>
       </c>
       <c r="H273" t="n">
-        <v>9.69</v>
+        <v>9.7</v>
       </c>
       <c r="I273" t="s">
         <v>13</v>
@@ -10185,7 +10185,7 @@
         <v>308</v>
       </c>
       <c r="E274" t="n">
-        <v>0.785296983164896</v>
+        <v>0.785091299308265</v>
       </c>
       <c r="F274" t="n">
         <v>1.84</v>
@@ -10194,7 +10194,7 @@
         <v>5.38</v>
       </c>
       <c r="H274" t="n">
-        <v>22.06</v>
+        <v>22.07</v>
       </c>
       <c r="I274" t="s">
         <v>13</v>
@@ -10217,7 +10217,7 @@
         <v>309</v>
       </c>
       <c r="E275" t="n">
-        <v>0.747233256898225</v>
+        <v>0.746989847553368</v>
       </c>
       <c r="F275" t="n">
         <v>1.9</v>
@@ -10226,7 +10226,7 @@
         <v>5.8</v>
       </c>
       <c r="H275" t="n">
-        <v>24.91</v>
+        <v>24.93</v>
       </c>
       <c r="I275" t="s">
         <v>13</v>
@@ -10249,7 +10249,7 @@
         <v>310</v>
       </c>
       <c r="E276" t="n">
-        <v>0.672490937144763</v>
+        <v>0.672145329925134</v>
       </c>
       <c r="F276" t="n">
         <v>2.04</v>
@@ -10258,7 +10258,7 @@
         <v>6.84</v>
       </c>
       <c r="H276" t="n">
-        <v>32.38</v>
+        <v>32.42</v>
       </c>
       <c r="I276" t="s">
         <v>13</v>
@@ -10281,7 +10281,7 @@
         <v>311</v>
       </c>
       <c r="E277" t="n">
-        <v>0.625189794775749</v>
+        <v>0.624988456035141</v>
       </c>
       <c r="F277" t="n">
         <v>2.15</v>
@@ -10290,7 +10290,7 @@
         <v>7.68</v>
       </c>
       <c r="H277" t="n">
-        <v>38.95</v>
+        <v>38.98</v>
       </c>
       <c r="I277" t="s">
         <v>13</v>
@@ -10313,16 +10313,16 @@
         <v>312</v>
       </c>
       <c r="E278" t="n">
-        <v>0.481425684394617</v>
+        <v>0.481510216309465</v>
       </c>
       <c r="F278" t="n">
         <v>2.62</v>
       </c>
       <c r="G278" t="n">
-        <v>11.82</v>
+        <v>11.81</v>
       </c>
       <c r="H278" t="n">
-        <v>76.81</v>
+        <v>76.78</v>
       </c>
       <c r="I278" t="s">
         <v>13</v>
@@ -10345,16 +10345,16 @@
         <v>313</v>
       </c>
       <c r="E279" t="n">
-        <v>0.478462849765252</v>
+        <v>0.478270951530946</v>
       </c>
       <c r="F279" t="n">
         <v>2.63</v>
       </c>
       <c r="G279" t="n">
-        <v>11.94</v>
+        <v>11.95</v>
       </c>
       <c r="H279" t="n">
-        <v>78.08</v>
+        <v>78.16</v>
       </c>
       <c r="I279" t="s">
         <v>13</v>
@@ -10377,7 +10377,7 @@
         <v>314</v>
       </c>
       <c r="E280" t="n">
-        <v>0.449648765531202</v>
+        <v>0.449720803137487</v>
       </c>
       <c r="F280" t="n">
         <v>2.76</v>
@@ -10386,7 +10386,7 @@
         <v>13.27</v>
       </c>
       <c r="H280" t="n">
-        <v>92.11</v>
+        <v>92.07</v>
       </c>
       <c r="I280" t="s">
         <v>13</v>
@@ -10409,7 +10409,7 @@
         <v>315</v>
       </c>
       <c r="E281" t="n">
-        <v>0.367989052548869</v>
+        <v>0.368033791247972</v>
       </c>
       <c r="F281" t="n">
         <v>3.25</v>
@@ -10418,7 +10418,7 @@
         <v>18.8</v>
       </c>
       <c r="H281" t="n">
-        <v>158.26</v>
+        <v>158.21</v>
       </c>
       <c r="I281" t="s">
         <v>13</v>
@@ -10441,16 +10441,16 @@
         <v>316</v>
       </c>
       <c r="E282" t="n">
-        <v>0.272652167368099</v>
+        <v>0.27271073101269</v>
       </c>
       <c r="F282" t="n">
         <v>4.19</v>
       </c>
       <c r="G282" t="n">
-        <v>32.2</v>
+        <v>32.19</v>
       </c>
       <c r="H282" t="n">
-        <v>362.68</v>
+        <v>362.46</v>
       </c>
       <c r="I282" t="s">
         <v>13</v>
@@ -10473,16 +10473,16 @@
         <v>317</v>
       </c>
       <c r="E283" t="n">
-        <v>0.244698178945097</v>
+        <v>0.244766165386477</v>
       </c>
       <c r="F283" t="n">
         <v>4.61</v>
       </c>
       <c r="G283" t="n">
-        <v>39.25</v>
+        <v>39.23</v>
       </c>
       <c r="H283" t="n">
-        <v>491.44</v>
+        <v>491.05</v>
       </c>
       <c r="I283" t="s">
         <v>13</v>
@@ -10505,16 +10505,16 @@
         <v>318</v>
       </c>
       <c r="E284" t="n">
-        <v>0.203874990749161</v>
+        <v>0.20392330338158</v>
       </c>
       <c r="F284" t="n">
         <v>5.42</v>
       </c>
       <c r="G284" t="n">
-        <v>55.06</v>
+        <v>55.03</v>
       </c>
       <c r="H284" t="n">
-        <v>824.37</v>
+        <v>823.82</v>
       </c>
       <c r="I284" t="s">
         <v>13</v>
@@ -10537,16 +10537,16 @@
         <v>319</v>
       </c>
       <c r="E285" t="n">
-        <v>0.203443682411806</v>
+        <v>0.203488089803904</v>
       </c>
       <c r="F285" t="n">
         <v>5.43</v>
       </c>
       <c r="G285" t="n">
-        <v>55.28</v>
+        <v>55.25</v>
       </c>
       <c r="H285" t="n">
-        <v>829.36</v>
+        <v>828.85</v>
       </c>
       <c r="I285" t="s">
         <v>13</v>
@@ -10569,16 +10569,16 @@
         <v>320</v>
       </c>
       <c r="E286" t="n">
-        <v>0.195669332038594</v>
+        <v>0.195709511127684</v>
       </c>
       <c r="F286" t="n">
         <v>5.63</v>
       </c>
       <c r="G286" t="n">
-        <v>59.45</v>
+        <v>59.43</v>
       </c>
       <c r="H286" t="n">
-        <v>926.83</v>
+        <v>926.29</v>
       </c>
       <c r="I286" t="s">
         <v>13</v>
@@ -10601,16 +10601,16 @@
         <v>321</v>
       </c>
       <c r="E287" t="n">
-        <v>0.12155781479894</v>
+        <v>0.121572593332329</v>
       </c>
       <c r="F287" t="n">
         <v>8.74</v>
       </c>
       <c r="G287" t="n">
-        <v>146.72</v>
+        <v>146.68</v>
       </c>
       <c r="H287" t="n">
-        <v>3658.27</v>
+        <v>3656.97</v>
       </c>
       <c r="I287" t="s">
         <v>13</v>
@@ -10633,16 +10633,16 @@
         <v>322</v>
       </c>
       <c r="E288" t="n">
-        <v>0.0768989245880054</v>
+        <v>0.0769082736646277</v>
       </c>
       <c r="F288" t="n">
         <v>13.51</v>
       </c>
       <c r="G288" t="n">
-        <v>355.94</v>
+        <v>355.86</v>
       </c>
       <c r="H288" t="n">
-        <v>13976.22</v>
+        <v>13971.22</v>
       </c>
       <c r="I288" t="s">
         <v>13</v>
@@ -10665,16 +10665,16 @@
         <v>323</v>
       </c>
       <c r="E289" t="n">
-        <v>0.0677473185775347</v>
+        <v>0.0677555550369616</v>
       </c>
       <c r="F289" t="n">
-        <v>15.27</v>
+        <v>15.26</v>
       </c>
       <c r="G289" t="n">
-        <v>455.83</v>
+        <v>455.72</v>
       </c>
       <c r="H289" t="n">
-        <v>20300.38</v>
+        <v>20293.1</v>
       </c>
       <c r="I289" t="s">
         <v>13</v>
@@ -10697,16 +10697,16 @@
         <v>326</v>
       </c>
       <c r="E290" t="n">
-        <v>1.86096612342587</v>
+        <v>1.81536548987418</v>
       </c>
       <c r="F290" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="G290" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="H290" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="I290" t="s">
         <v>13</v>
@@ -10729,16 +10729,16 @@
         <v>327</v>
       </c>
       <c r="E291" t="n">
-        <v>1.25185026789793</v>
+        <v>1.22101447383971</v>
       </c>
       <c r="F291" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G291" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="H291" t="n">
-        <v>7.58</v>
+        <v>7.99</v>
       </c>
       <c r="I291" t="s">
         <v>13</v>
@@ -10761,16 +10761,16 @@
         <v>328</v>
       </c>
       <c r="E292" t="n">
-        <v>1.24782576746853</v>
+        <v>1.21715479520353</v>
       </c>
       <c r="F292" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G292" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="H292" t="n">
-        <v>7.63</v>
+        <v>8.05</v>
       </c>
       <c r="I292" t="s">
         <v>13</v>
@@ -10793,16 +10793,16 @@
         <v>329</v>
       </c>
       <c r="E293" t="n">
-        <v>1.00155872550557</v>
+        <v>0.976877028752093</v>
       </c>
       <c r="F293" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G293" t="n">
-        <v>3.78</v>
+        <v>3.91</v>
       </c>
       <c r="H293" t="n">
-        <v>12.41</v>
+        <v>13.14</v>
       </c>
       <c r="I293" t="s">
         <v>13</v>
@@ -10825,16 +10825,16 @@
         <v>330</v>
       </c>
       <c r="E294" t="n">
-        <v>0.968474320817879</v>
+        <v>0.944610840509643</v>
       </c>
       <c r="F294" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="G294" t="n">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="H294" t="n">
-        <v>13.41</v>
+        <v>14.2</v>
       </c>
       <c r="I294" t="s">
         <v>13</v>
@@ -10857,16 +10857,16 @@
         <v>331</v>
       </c>
       <c r="E295" t="n">
-        <v>0.816656286644668</v>
+        <v>0.79638904221632</v>
       </c>
       <c r="F295" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G295" t="n">
-        <v>5.07</v>
+        <v>5.27</v>
       </c>
       <c r="H295" t="n">
-        <v>20.06</v>
+        <v>21.32</v>
       </c>
       <c r="I295" t="s">
         <v>13</v>
@@ -10889,16 +10889,16 @@
         <v>332</v>
       </c>
       <c r="E296" t="n">
-        <v>0.719028594508128</v>
+        <v>0.701029579228959</v>
       </c>
       <c r="F296" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="G296" t="n">
-        <v>6.16</v>
+        <v>6.4</v>
       </c>
       <c r="H296" t="n">
-        <v>27.4</v>
+        <v>29.18</v>
       </c>
       <c r="I296" t="s">
         <v>13</v>
@@ -10921,16 +10921,16 @@
         <v>333</v>
       </c>
       <c r="E297" t="n">
-        <v>0.616490657094091</v>
+        <v>0.600989739361392</v>
       </c>
       <c r="F297" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="G297" t="n">
-        <v>7.85</v>
+        <v>8.18</v>
       </c>
       <c r="H297" t="n">
-        <v>40.36</v>
+        <v>43.08</v>
       </c>
       <c r="I297" t="s">
         <v>13</v>
@@ -10953,16 +10953,16 @@
         <v>334</v>
       </c>
       <c r="E298" t="n">
-        <v>0.614689170315651</v>
+        <v>0.599454864533561</v>
       </c>
       <c r="F298" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G298" t="n">
-        <v>7.89</v>
+        <v>8.22</v>
       </c>
       <c r="H298" t="n">
-        <v>40.66</v>
+        <v>43.36</v>
       </c>
       <c r="I298" t="s">
         <v>13</v>
@@ -10985,16 +10985,16 @@
         <v>335</v>
       </c>
       <c r="E299" t="n">
-        <v>0.395892846181636</v>
+        <v>0.386268322254537</v>
       </c>
       <c r="F299" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="G299" t="n">
-        <v>16.54</v>
+        <v>17.27</v>
       </c>
       <c r="H299" t="n">
-        <v>129.74</v>
+        <v>138.69</v>
       </c>
       <c r="I299" t="s">
         <v>13</v>
@@ -11017,16 +11017,16 @@
         <v>336</v>
       </c>
       <c r="E300" t="n">
-        <v>0.387002497248311</v>
+        <v>0.377580533683244</v>
       </c>
       <c r="F300" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="G300" t="n">
-        <v>17.21</v>
+        <v>17.97</v>
       </c>
       <c r="H300" t="n">
-        <v>137.98</v>
+        <v>147.54</v>
       </c>
       <c r="I300" t="s">
         <v>13</v>
@@ -11049,16 +11049,16 @@
         <v>337</v>
       </c>
       <c r="E301" t="n">
-        <v>0.333624891143899</v>
+        <v>0.325487851397059</v>
       </c>
       <c r="F301" t="n">
-        <v>3.53</v>
+        <v>3.6</v>
       </c>
       <c r="G301" t="n">
-        <v>22.37</v>
+        <v>23.38</v>
       </c>
       <c r="H301" t="n">
-        <v>207.07</v>
+        <v>221.66</v>
       </c>
       <c r="I301" t="s">
         <v>13</v>
@@ -11081,16 +11081,16 @@
         <v>338</v>
       </c>
       <c r="E302" t="n">
-        <v>0.315862596480076</v>
+        <v>0.30819556878488</v>
       </c>
       <c r="F302" t="n">
-        <v>3.69</v>
+        <v>3.77</v>
       </c>
       <c r="G302" t="n">
-        <v>24.68</v>
+        <v>25.79</v>
       </c>
       <c r="H302" t="n">
-        <v>240.83</v>
+        <v>257.79</v>
       </c>
       <c r="I302" t="s">
         <v>13</v>
@@ -11113,16 +11113,16 @@
         <v>339</v>
       </c>
       <c r="E303" t="n">
-        <v>0.305243197376736</v>
+        <v>0.297816523319685</v>
       </c>
       <c r="F303" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="G303" t="n">
-        <v>26.24</v>
+        <v>27.43</v>
       </c>
       <c r="H303" t="n">
-        <v>264.77</v>
+        <v>283.51</v>
       </c>
       <c r="I303" t="s">
         <v>13</v>
@@ -11145,16 +11145,16 @@
         <v>340</v>
       </c>
       <c r="E304" t="n">
-        <v>0.221068817937892</v>
+        <v>0.215710694721296</v>
       </c>
       <c r="F304" t="n">
-        <v>5.04</v>
+        <v>5.15</v>
       </c>
       <c r="G304" t="n">
-        <v>47.36</v>
+        <v>49.56</v>
       </c>
       <c r="H304" t="n">
-        <v>654.9</v>
+        <v>702.12</v>
       </c>
       <c r="I304" t="s">
         <v>13</v>
@@ -11177,16 +11177,16 @@
         <v>341</v>
       </c>
       <c r="E305" t="n">
-        <v>0.217605453160496</v>
+        <v>0.212298102694453</v>
       </c>
       <c r="F305" t="n">
-        <v>5.11</v>
+        <v>5.23</v>
       </c>
       <c r="G305" t="n">
-        <v>48.77</v>
+        <v>51.06</v>
       </c>
       <c r="H305" t="n">
-        <v>684.9</v>
+        <v>734.67</v>
       </c>
       <c r="I305" t="s">
         <v>13</v>
@@ -11209,16 +11209,16 @@
         <v>342</v>
       </c>
       <c r="E306" t="n">
-        <v>0.178458335721854</v>
+        <v>0.174105775078238</v>
       </c>
       <c r="F306" t="n">
-        <v>6.12</v>
+        <v>6.26</v>
       </c>
       <c r="G306" t="n">
-        <v>70.67</v>
+        <v>74.04</v>
       </c>
       <c r="H306" t="n">
-        <v>1206.16</v>
+        <v>1294.71</v>
       </c>
       <c r="I306" t="s">
         <v>13</v>
@@ -11241,16 +11241,16 @@
         <v>343</v>
       </c>
       <c r="E307" t="n">
-        <v>0.162274997052931</v>
+        <v>0.158317144578523</v>
       </c>
       <c r="F307" t="n">
-        <v>6.68</v>
+        <v>6.83</v>
       </c>
       <c r="G307" t="n">
-        <v>84.56</v>
+        <v>88.61</v>
       </c>
       <c r="H307" t="n">
-        <v>1585.03</v>
+        <v>1701.88</v>
       </c>
       <c r="I307" t="s">
         <v>13</v>
@@ -11273,16 +11273,16 @@
         <v>345</v>
       </c>
       <c r="E308" t="n">
-        <v>1.98005075396349</v>
+        <v>1.93455095073635</v>
       </c>
       <c r="F308" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G308" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="H308" t="n">
-        <v>3.15</v>
+        <v>3.27</v>
       </c>
       <c r="I308" t="s">
         <v>13</v>
@@ -11305,16 +11305,16 @@
         <v>346</v>
       </c>
       <c r="E309" t="n">
-        <v>1.70260948862147</v>
+        <v>1.66344781327</v>
       </c>
       <c r="F309" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="G309" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="H309" t="n">
-        <v>4.11</v>
+        <v>4.29</v>
       </c>
       <c r="I309" t="s">
         <v>13</v>
@@ -11337,16 +11337,16 @@
         <v>347</v>
       </c>
       <c r="E310" t="n">
-        <v>1.29104921760654</v>
+        <v>1.26114271815592</v>
       </c>
       <c r="F310" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="G310" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="H310" t="n">
-        <v>7.1</v>
+        <v>7.46</v>
       </c>
       <c r="I310" t="s">
         <v>13</v>
@@ -11369,16 +11369,16 @@
         <v>348</v>
       </c>
       <c r="E311" t="n">
-        <v>1.20894590116844</v>
+        <v>1.18105368337449</v>
       </c>
       <c r="F311" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G311" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="H311" t="n">
-        <v>8.17</v>
+        <v>8.59</v>
       </c>
       <c r="I311" t="s">
         <v>13</v>
@@ -11401,16 +11401,16 @@
         <v>349</v>
       </c>
       <c r="E312" t="n">
-        <v>0.896492582508448</v>
+        <v>0.875432980879889</v>
       </c>
       <c r="F312" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G312" t="n">
-        <v>4.42</v>
+        <v>4.58</v>
       </c>
       <c r="H312" t="n">
-        <v>16.06</v>
+        <v>16.99</v>
       </c>
       <c r="I312" t="s">
         <v>13</v>
@@ -11433,16 +11433,16 @@
         <v>350</v>
       </c>
       <c r="E313" t="n">
-        <v>0.867529096700234</v>
+        <v>0.847452680333655</v>
       </c>
       <c r="F313" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="G313" t="n">
-        <v>4.64</v>
+        <v>4.8</v>
       </c>
       <c r="H313" t="n">
-        <v>17.36</v>
+        <v>18.35</v>
       </c>
       <c r="I313" t="s">
         <v>13</v>
@@ -11465,16 +11465,16 @@
         <v>351</v>
       </c>
       <c r="E314" t="n">
-        <v>0.852225718298369</v>
+        <v>0.832457252330545</v>
       </c>
       <c r="F314" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="G314" t="n">
-        <v>4.76</v>
+        <v>4.93</v>
       </c>
       <c r="H314" t="n">
-        <v>18.11</v>
+        <v>19.16</v>
       </c>
       <c r="I314" t="s">
         <v>13</v>
@@ -11497,16 +11497,16 @@
         <v>352</v>
       </c>
       <c r="E315" t="n">
-        <v>0.797625734234429</v>
+        <v>0.779002510379363</v>
       </c>
       <c r="F315" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="G315" t="n">
-        <v>5.25</v>
+        <v>5.44</v>
       </c>
       <c r="H315" t="n">
-        <v>21.24</v>
+        <v>22.5</v>
       </c>
       <c r="I315" t="s">
         <v>13</v>
@@ -11529,16 +11529,16 @@
         <v>353</v>
       </c>
       <c r="E316" t="n">
-        <v>0.422381209722972</v>
+        <v>0.412768829247086</v>
       </c>
       <c r="F316" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="G316" t="n">
-        <v>14.78</v>
+        <v>15.38</v>
       </c>
       <c r="H316" t="n">
-        <v>108.93</v>
+        <v>115.89</v>
       </c>
       <c r="I316" t="s">
         <v>13</v>
@@ -11561,16 +11561,16 @@
         <v>354</v>
       </c>
       <c r="E317" t="n">
-        <v>0.390197110146304</v>
+        <v>0.381332147663718</v>
       </c>
       <c r="F317" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G317" t="n">
-        <v>16.97</v>
+        <v>17.66</v>
       </c>
       <c r="H317" t="n">
-        <v>134.94</v>
+        <v>143.63</v>
       </c>
       <c r="I317" t="s">
         <v>13</v>
@@ -11593,16 +11593,16 @@
         <v>355</v>
       </c>
       <c r="E318" t="n">
-        <v>0.384163395850136</v>
+        <v>0.375427006031127</v>
       </c>
       <c r="F318" t="n">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="G318" t="n">
-        <v>17.43</v>
+        <v>18.15</v>
       </c>
       <c r="H318" t="n">
-        <v>140.77</v>
+        <v>149.86</v>
       </c>
       <c r="I318" t="s">
         <v>13</v>
@@ -11625,16 +11625,16 @@
         <v>356</v>
       </c>
       <c r="E319" t="n">
-        <v>0.381171637485118</v>
+        <v>0.372498966052036</v>
       </c>
       <c r="F319" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="G319" t="n">
-        <v>17.68</v>
+        <v>18.4</v>
       </c>
       <c r="H319" t="n">
-        <v>143.79</v>
+        <v>153.09</v>
       </c>
       <c r="I319" t="s">
         <v>13</v>
@@ -11657,16 +11657,16 @@
         <v>357</v>
       </c>
       <c r="E320" t="n">
-        <v>0.362195539227462</v>
+        <v>0.35395354861449</v>
       </c>
       <c r="F320" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="G320" t="n">
-        <v>19.34</v>
+        <v>20.14</v>
       </c>
       <c r="H320" t="n">
-        <v>165.27</v>
+        <v>176.02</v>
       </c>
       <c r="I320" t="s">
         <v>13</v>
@@ -11689,16 +11689,16 @@
         <v>358</v>
       </c>
       <c r="E321" t="n">
-        <v>0.275227979374437</v>
+        <v>0.2689694996698</v>
       </c>
       <c r="F321" t="n">
-        <v>4.16</v>
+        <v>4.24</v>
       </c>
       <c r="G321" t="n">
-        <v>31.65</v>
+        <v>33.01</v>
       </c>
       <c r="H321" t="n">
-        <v>353.26</v>
+        <v>376.75</v>
       </c>
       <c r="I321" t="s">
         <v>13</v>
@@ -11721,16 +11721,16 @@
         <v>359</v>
       </c>
       <c r="E322" t="n">
-        <v>0.253094582060752</v>
+        <v>0.247320625075239</v>
       </c>
       <c r="F322" t="n">
-        <v>4.47</v>
+        <v>4.56</v>
       </c>
       <c r="G322" t="n">
-        <v>36.89</v>
+        <v>38.49</v>
       </c>
       <c r="H322" t="n">
-        <v>446.9</v>
+        <v>476.9</v>
       </c>
       <c r="I322" t="s">
         <v>13</v>
@@ -11753,16 +11753,16 @@
         <v>360</v>
       </c>
       <c r="E323" t="n">
-        <v>0.188068627855267</v>
+        <v>0.183803074897027</v>
       </c>
       <c r="F323" t="n">
-        <v>5.83</v>
+        <v>5.96</v>
       </c>
       <c r="G323" t="n">
-        <v>64.04</v>
+        <v>66.85</v>
       </c>
       <c r="H323" t="n">
-        <v>1037.93</v>
+        <v>1108.37</v>
       </c>
       <c r="I323" t="s">
         <v>13</v>
@@ -11785,16 +11785,16 @@
         <v>361</v>
       </c>
       <c r="E324" t="n">
-        <v>0.159145366125726</v>
+        <v>0.155514713541338</v>
       </c>
       <c r="F324" t="n">
-        <v>6.8</v>
+        <v>6.94</v>
       </c>
       <c r="G324" t="n">
-        <v>87.74</v>
+        <v>91.67</v>
       </c>
       <c r="H324" t="n">
-        <v>1676.48</v>
+        <v>1791.81</v>
       </c>
       <c r="I324" t="s">
         <v>13</v>
@@ -11817,16 +11817,16 @@
         <v>362</v>
       </c>
       <c r="E325" t="n">
-        <v>0.0902156604166001</v>
+        <v>0.0881575312443999</v>
       </c>
       <c r="F325" t="n">
-        <v>11.59</v>
+        <v>11.85</v>
       </c>
       <c r="G325" t="n">
-        <v>260.91</v>
+        <v>272.86</v>
       </c>
       <c r="H325" t="n">
-        <v>8742.27</v>
+        <v>9354.58</v>
       </c>
       <c r="I325" t="s">
         <v>13</v>
